--- a/research/traditional_assets/database/data/taiwan/taiwan_advertising.xlsx
+++ b/research/traditional_assets/database/data/taiwan/taiwan_advertising.xlsx
@@ -1406,7 +1406,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1543,22 +1543,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1082492089411281</v>
+        <v>0.1080687105232458</v>
       </c>
       <c r="C2">
-        <v>91.88465909028186</v>
+        <v>91.12336312819096</v>
       </c>
       <c r="D2">
-        <v>77.18465909028185</v>
+        <v>77.34346312819096</v>
       </c>
       <c r="E2">
-        <v>-1.41</v>
+        <v>-0.4899</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.9200999999999999</v>
       </c>
       <c r="G2">
         <v>14.7</v>
@@ -1579,28 +1579,28 @@
         <v>9.9</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.04628102999999999</v>
       </c>
       <c r="N2">
-        <v>9.9</v>
+        <v>9.853718970000001</v>
       </c>
       <c r="O2">
-        <v>1.98</v>
+        <v>1.970743794</v>
       </c>
       <c r="P2">
-        <v>7.92</v>
+        <v>7.882975176</v>
       </c>
       <c r="Q2">
-        <v>8.619999999999999</v>
+        <v>8.582975176</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1082492089411281</v>
+        <v>0.1087538490133796</v>
       </c>
       <c r="T2">
-        <v>1.217251318914063</v>
+        <v>1.227087693208318</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>213.9105374275379</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1625,22 +1625,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1080687105232458</v>
+        <v>0.1078882121053635</v>
       </c>
       <c r="C3">
-        <v>91.12336312819096</v>
+        <v>90.36272197797953</v>
       </c>
       <c r="D3">
-        <v>77.34346312819096</v>
+        <v>77.50292197797953</v>
       </c>
       <c r="E3">
-        <v>-0.4899</v>
+        <v>0.4301999999999999</v>
       </c>
       <c r="F3">
-        <v>0.9200999999999999</v>
+        <v>1.8402</v>
       </c>
       <c r="G3">
         <v>14.7</v>
@@ -1661,28 +1661,28 @@
         <v>9.9</v>
       </c>
       <c r="M3">
-        <v>0.04628102999999999</v>
+        <v>0.09256205999999999</v>
       </c>
       <c r="N3">
-        <v>9.853718970000001</v>
+        <v>9.80743794</v>
       </c>
       <c r="O3">
-        <v>1.970743794</v>
+        <v>1.961487588</v>
       </c>
       <c r="P3">
-        <v>7.882975176</v>
+        <v>7.845950352</v>
       </c>
       <c r="Q3">
-        <v>8.582975176</v>
+        <v>8.545950351999998</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1087538490133796</v>
+        <v>0.1092687878626159</v>
       </c>
       <c r="T3">
-        <v>1.227087693208318</v>
+        <v>1.237124809835109</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>213.9105374275379</v>
+        <v>106.9552687137689</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1707,22 +1707,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1078882121053635</v>
+        <v>0.1077077136874813</v>
       </c>
       <c r="C4">
-        <v>90.36272197797953</v>
+        <v>89.60273969808746</v>
       </c>
       <c r="D4">
-        <v>77.50292197797953</v>
+        <v>77.66303969808746</v>
       </c>
       <c r="E4">
-        <v>0.4301999999999999</v>
+        <v>1.3503</v>
       </c>
       <c r="F4">
-        <v>1.8402</v>
+        <v>2.7603</v>
       </c>
       <c r="G4">
         <v>14.7</v>
@@ -1743,28 +1743,28 @@
         <v>9.9</v>
       </c>
       <c r="M4">
-        <v>0.09256205999999999</v>
+        <v>0.13884309</v>
       </c>
       <c r="N4">
-        <v>9.80743794</v>
+        <v>9.76115691</v>
       </c>
       <c r="O4">
-        <v>1.961487588</v>
+        <v>1.952231382</v>
       </c>
       <c r="P4">
-        <v>7.845950352</v>
+        <v>7.808925528000001</v>
       </c>
       <c r="Q4">
-        <v>8.545950351999998</v>
+        <v>8.508925527999999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1092687878626159</v>
+        <v>0.1097943440077127</v>
       </c>
       <c r="T4">
-        <v>1.237124809835109</v>
+        <v>1.247368877320184</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>106.9552687137689</v>
+        <v>71.30351247584595</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1789,22 +1789,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1077077136874813</v>
+        <v>0.1075272152695991</v>
       </c>
       <c r="C5">
-        <v>89.60273969808746</v>
+        <v>88.84342038056245</v>
       </c>
       <c r="D5">
-        <v>77.66303969808746</v>
+        <v>77.82382038056245</v>
       </c>
       <c r="E5">
-        <v>1.3503</v>
+        <v>2.2704</v>
       </c>
       <c r="F5">
-        <v>2.7603</v>
+        <v>3.6804</v>
       </c>
       <c r="G5">
         <v>14.7</v>
@@ -1825,28 +1825,28 @@
         <v>9.9</v>
       </c>
       <c r="M5">
-        <v>0.13884309</v>
+        <v>0.18512412</v>
       </c>
       <c r="N5">
-        <v>9.76115691</v>
+        <v>9.714875880000001</v>
       </c>
       <c r="O5">
-        <v>1.952231382</v>
+        <v>1.942975176</v>
       </c>
       <c r="P5">
-        <v>7.808925528000001</v>
+        <v>7.771900704000001</v>
       </c>
       <c r="Q5">
-        <v>8.508925527999999</v>
+        <v>8.471900703999999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1097943440077127</v>
+        <v>0.1103308492391657</v>
       </c>
       <c r="T5">
-        <v>1.247368877320184</v>
+        <v>1.257826362877865</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>71.30351247584595</v>
+        <v>53.47763435688447</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1871,22 +1871,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1075272152695991</v>
+        <v>0.1073467168517168</v>
       </c>
       <c r="C6">
-        <v>88.84342038056245</v>
+        <v>88.08476815140845</v>
       </c>
       <c r="D6">
-        <v>77.82382038056245</v>
+        <v>77.98526815140845</v>
       </c>
       <c r="E6">
-        <v>2.2704</v>
+        <v>3.190499999999999</v>
       </c>
       <c r="F6">
-        <v>3.6804</v>
+        <v>4.600499999999999</v>
       </c>
       <c r="G6">
         <v>14.7</v>
@@ -1907,28 +1907,28 @@
         <v>9.9</v>
       </c>
       <c r="M6">
-        <v>0.18512412</v>
+        <v>0.2314051499999999</v>
       </c>
       <c r="N6">
-        <v>9.714875880000001</v>
+        <v>9.66859485</v>
       </c>
       <c r="O6">
-        <v>1.942975176</v>
+        <v>1.93371897</v>
       </c>
       <c r="P6">
-        <v>7.771900704000001</v>
+        <v>7.73487588</v>
       </c>
       <c r="Q6">
-        <v>8.471900703999999</v>
+        <v>8.43487588</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1103308492391657</v>
+        <v>0.1108786493175966</v>
       </c>
       <c r="T6">
-        <v>1.257826362877865</v>
+        <v>1.268504006026234</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>53.47763435688447</v>
+        <v>42.78210748550757</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1953,22 +1953,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1073467168517168</v>
+        <v>0.1071662184338345</v>
       </c>
       <c r="C7">
-        <v>88.08476815140845</v>
+        <v>87.32678717093859</v>
       </c>
       <c r="D7">
-        <v>77.98526815140845</v>
+        <v>78.14738717093859</v>
       </c>
       <c r="E7">
-        <v>3.190499999999999</v>
+        <v>4.1106</v>
       </c>
       <c r="F7">
-        <v>4.600499999999999</v>
+        <v>5.5206</v>
       </c>
       <c r="G7">
         <v>14.7</v>
@@ -1989,28 +1989,28 @@
         <v>9.9</v>
       </c>
       <c r="M7">
-        <v>0.2314051499999999</v>
+        <v>0.27768618</v>
       </c>
       <c r="N7">
-        <v>9.66859485</v>
+        <v>9.62231382</v>
       </c>
       <c r="O7">
-        <v>1.93371897</v>
+        <v>1.924462764</v>
       </c>
       <c r="P7">
-        <v>7.73487588</v>
+        <v>7.697851056</v>
       </c>
       <c r="Q7">
-        <v>8.43487588</v>
+        <v>8.397851056</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1108786493175966</v>
+        <v>0.1114381047168453</v>
       </c>
       <c r="T7">
-        <v>1.268504006026234</v>
+        <v>1.279408833071377</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>42.78210748550757</v>
+        <v>35.65175623792297</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2035,22 +2035,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1071662184338345</v>
+        <v>0.1069857200159523</v>
       </c>
       <c r="C8">
-        <v>87.32678717093859</v>
+        <v>86.56948163413263</v>
       </c>
       <c r="D8">
-        <v>78.14738717093859</v>
+        <v>78.31018163413262</v>
       </c>
       <c r="E8">
-        <v>4.110599999999999</v>
+        <v>5.030699999999999</v>
       </c>
       <c r="F8">
-        <v>5.520599999999999</v>
+        <v>6.440699999999999</v>
       </c>
       <c r="G8">
         <v>14.7</v>
@@ -2071,28 +2071,28 @@
         <v>9.9</v>
       </c>
       <c r="M8">
-        <v>0.2776861799999999</v>
+        <v>0.3239672099999999</v>
       </c>
       <c r="N8">
-        <v>9.62231382</v>
+        <v>9.576032790000001</v>
       </c>
       <c r="O8">
-        <v>1.924462764</v>
+        <v>1.915206558</v>
       </c>
       <c r="P8">
-        <v>7.697851056</v>
+        <v>7.660826232000001</v>
       </c>
       <c r="Q8">
-        <v>8.397851056</v>
+        <v>8.360826232000001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1114381047168453</v>
+        <v>0.1120095914150025</v>
       </c>
       <c r="T8">
-        <v>1.279408833071377</v>
+        <v>1.290548172526093</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>35.65175623792297</v>
+        <v>30.55864820393398</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2117,22 +2117,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1069857200159523</v>
+        <v>0.10680522159807</v>
       </c>
       <c r="C9">
-        <v>86.56948163413261</v>
+        <v>85.81285577099877</v>
       </c>
       <c r="D9">
-        <v>78.31018163413262</v>
+        <v>78.47365577099876</v>
       </c>
       <c r="E9">
-        <v>5.0307</v>
+        <v>5.950799999999999</v>
       </c>
       <c r="F9">
-        <v>6.4407</v>
+        <v>7.360799999999999</v>
       </c>
       <c r="G9">
         <v>14.7</v>
@@ -2153,28 +2153,28 @@
         <v>9.9</v>
       </c>
       <c r="M9">
-        <v>0.3239672099999999</v>
+        <v>0.37024824</v>
       </c>
       <c r="N9">
-        <v>9.576032790000001</v>
+        <v>9.52975176</v>
       </c>
       <c r="O9">
-        <v>1.915206558</v>
+        <v>1.905950352</v>
       </c>
       <c r="P9">
-        <v>7.660826232000001</v>
+        <v>7.623801408</v>
       </c>
       <c r="Q9">
-        <v>8.360826232000001</v>
+        <v>8.323801408</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1120095914150025</v>
+        <v>0.1125935017370326</v>
       </c>
       <c r="T9">
-        <v>1.290548172526093</v>
+        <v>1.301929671534171</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>30.55864820393398</v>
+        <v>26.73881717844223</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2199,22 +2199,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.10680522159807</v>
+        <v>0.1066247231801878</v>
       </c>
       <c r="C10">
-        <v>85.81285577099877</v>
+        <v>85.05691384694002</v>
       </c>
       <c r="D10">
-        <v>78.47365577099876</v>
+        <v>78.63781384694002</v>
       </c>
       <c r="E10">
-        <v>5.950799999999999</v>
+        <v>6.870899999999999</v>
       </c>
       <c r="F10">
-        <v>7.360799999999999</v>
+        <v>8.280899999999999</v>
       </c>
       <c r="G10">
         <v>14.7</v>
@@ -2235,28 +2235,28 @@
         <v>9.9</v>
       </c>
       <c r="M10">
-        <v>0.37024824</v>
+        <v>0.41652927</v>
       </c>
       <c r="N10">
-        <v>9.52975176</v>
+        <v>9.483470730000001</v>
       </c>
       <c r="O10">
-        <v>1.905950352</v>
+        <v>1.896694146</v>
       </c>
       <c r="P10">
-        <v>7.623801408</v>
+        <v>7.586776584000001</v>
       </c>
       <c r="Q10">
-        <v>8.323801408</v>
+        <v>8.286776584</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1125935017370326</v>
+        <v>0.1131902452529536</v>
       </c>
       <c r="T10">
-        <v>1.301929671534171</v>
+        <v>1.313561313377593</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>26.73881717844223</v>
+        <v>23.76783749194865</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2281,22 +2281,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1066247231801878</v>
+        <v>0.1064442247623055</v>
       </c>
       <c r="C11">
-        <v>85.05691384694002</v>
+        <v>84.30166016312522</v>
       </c>
       <c r="D11">
-        <v>78.63781384694002</v>
+        <v>78.80266016312521</v>
       </c>
       <c r="E11">
-        <v>6.870899999999999</v>
+        <v>7.790999999999999</v>
       </c>
       <c r="F11">
-        <v>8.280899999999999</v>
+        <v>9.200999999999999</v>
       </c>
       <c r="G11">
         <v>14.7</v>
@@ -2317,28 +2317,28 @@
         <v>9.9</v>
       </c>
       <c r="M11">
-        <v>0.41652927</v>
+        <v>0.4628102999999999</v>
       </c>
       <c r="N11">
-        <v>9.483470730000001</v>
+        <v>9.437189700000001</v>
       </c>
       <c r="O11">
-        <v>1.896694146</v>
+        <v>1.88743794</v>
       </c>
       <c r="P11">
-        <v>7.586776584000001</v>
+        <v>7.549751760000001</v>
       </c>
       <c r="Q11">
-        <v>8.286776584</v>
+        <v>8.249751760000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1131902452529536</v>
+        <v>0.113800249735895</v>
       </c>
       <c r="T11">
-        <v>1.313561313377593</v>
+        <v>1.325451436150868</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>23.76783749194865</v>
+        <v>21.39105374275379</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2363,22 +2363,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1064442247623055</v>
+        <v>0.1062637263444233</v>
       </c>
       <c r="C12">
-        <v>84.30166016312519</v>
+        <v>83.54709905686451</v>
       </c>
       <c r="D12">
-        <v>78.80266016312518</v>
+        <v>78.96819905686451</v>
       </c>
       <c r="E12">
-        <v>7.790999999999999</v>
+        <v>8.711099999999998</v>
       </c>
       <c r="F12">
-        <v>9.200999999999999</v>
+        <v>10.1211</v>
       </c>
       <c r="G12">
         <v>14.7</v>
@@ -2399,28 +2399,28 @@
         <v>9.9</v>
       </c>
       <c r="M12">
-        <v>0.4628102999999999</v>
+        <v>0.5090913299999998</v>
       </c>
       <c r="N12">
-        <v>9.437189700000001</v>
+        <v>9.39090867</v>
       </c>
       <c r="O12">
-        <v>1.88743794</v>
+        <v>1.878181734</v>
       </c>
       <c r="P12">
-        <v>7.549751760000001</v>
+        <v>7.512726936</v>
       </c>
       <c r="Q12">
-        <v>8.249751760000001</v>
+        <v>8.212726935999999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.113800249735895</v>
+        <v>0.1144239621847452</v>
       </c>
       <c r="T12">
-        <v>1.325451436150868</v>
+        <v>1.33760875269433</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>21.39105374275379</v>
+        <v>19.44641249341253</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1062637263444233</v>
+        <v>0.106083227926541</v>
       </c>
       <c r="C13">
-        <v>83.54709905686451</v>
+        <v>82.79323490199009</v>
       </c>
       <c r="D13">
-        <v>78.96819905686451</v>
+        <v>79.13443490199009</v>
       </c>
       <c r="E13">
-        <v>8.711099999999998</v>
+        <v>9.631199999999998</v>
       </c>
       <c r="F13">
-        <v>10.1211</v>
+        <v>11.0412</v>
       </c>
       <c r="G13">
         <v>14.7</v>
@@ -2481,28 +2481,28 @@
         <v>9.9</v>
       </c>
       <c r="M13">
-        <v>0.5090913299999998</v>
+        <v>0.5553723599999999</v>
       </c>
       <c r="N13">
-        <v>9.39090867</v>
+        <v>9.344627640000001</v>
       </c>
       <c r="O13">
-        <v>1.878181734</v>
+        <v>1.868925528</v>
       </c>
       <c r="P13">
-        <v>7.512726936</v>
+        <v>7.475702112</v>
       </c>
       <c r="Q13">
-        <v>8.212726935999999</v>
+        <v>8.175702112</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1144239621847452</v>
+        <v>0.1150618499165239</v>
       </c>
       <c r="T13">
-        <v>1.33760875269433</v>
+        <v>1.350042371886506</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>19.44641249341253</v>
+        <v>17.82587811896149</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2527,22 +2527,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.106083227926541</v>
+        <v>0.1059027295086587</v>
       </c>
       <c r="C14">
-        <v>82.79323490199009</v>
+        <v>82.04007210924117</v>
       </c>
       <c r="D14">
-        <v>79.13443490199009</v>
+        <v>79.30137210924116</v>
       </c>
       <c r="E14">
-        <v>9.631199999999998</v>
+        <v>10.5513</v>
       </c>
       <c r="F14">
-        <v>11.0412</v>
+        <v>11.9613</v>
       </c>
       <c r="G14">
         <v>14.7</v>
@@ -2563,28 +2563,28 @@
         <v>9.9</v>
       </c>
       <c r="M14">
-        <v>0.5553723599999999</v>
+        <v>0.60165339</v>
       </c>
       <c r="N14">
-        <v>9.344627640000001</v>
+        <v>9.298346610000001</v>
       </c>
       <c r="O14">
-        <v>1.868925528</v>
+        <v>1.859669322</v>
       </c>
       <c r="P14">
-        <v>7.475702112</v>
+        <v>7.438677288000001</v>
       </c>
       <c r="Q14">
-        <v>8.175702112</v>
+        <v>8.138677288</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1150618499165239</v>
+        <v>0.1157144017340905</v>
       </c>
       <c r="T14">
-        <v>1.350042371886506</v>
+        <v>1.362761821404939</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>17.82587811896149</v>
+        <v>16.45465672519522</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2609,22 +2609,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1059027295086587</v>
+        <v>0.1057222310907765</v>
       </c>
       <c r="C15">
-        <v>82.04007210924117</v>
+        <v>81.28761512665406</v>
       </c>
       <c r="D15">
-        <v>79.30137210924116</v>
+        <v>79.46901512665406</v>
       </c>
       <c r="E15">
-        <v>10.5513</v>
+        <v>11.4714</v>
       </c>
       <c r="F15">
-        <v>11.9613</v>
+        <v>12.8814</v>
       </c>
       <c r="G15">
         <v>14.7</v>
@@ -2645,28 +2645,28 @@
         <v>9.9</v>
       </c>
       <c r="M15">
-        <v>0.60165339</v>
+        <v>0.6479344199999999</v>
       </c>
       <c r="N15">
-        <v>9.298346610000001</v>
+        <v>9.25206558</v>
       </c>
       <c r="O15">
-        <v>1.859669322</v>
+        <v>1.850413116</v>
       </c>
       <c r="P15">
-        <v>7.438677288000001</v>
+        <v>7.401652464</v>
       </c>
       <c r="Q15">
-        <v>8.138677288</v>
+        <v>8.101652463999999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1157144017340905</v>
+        <v>0.1163821291753215</v>
       </c>
       <c r="T15">
-        <v>1.362761821404939</v>
+        <v>1.375777072074964</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>16.45465672519522</v>
+        <v>15.27932410196699</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2691,22 +2691,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1057222310907765</v>
+        <v>0.1055417326728942</v>
       </c>
       <c r="C16">
-        <v>81.28761512665406</v>
+        <v>80.53586843995745</v>
       </c>
       <c r="D16">
-        <v>79.46901512665406</v>
+        <v>79.63736843995746</v>
       </c>
       <c r="E16">
-        <v>11.4714</v>
+        <v>12.3915</v>
       </c>
       <c r="F16">
-        <v>12.8814</v>
+        <v>13.8015</v>
       </c>
       <c r="G16">
         <v>14.7</v>
@@ -2727,28 +2727,28 @@
         <v>9.9</v>
       </c>
       <c r="M16">
-        <v>0.6479344199999999</v>
+        <v>0.69421545</v>
       </c>
       <c r="N16">
-        <v>9.25206558</v>
+        <v>9.205784550000001</v>
       </c>
       <c r="O16">
-        <v>1.850413116</v>
+        <v>1.84115691</v>
       </c>
       <c r="P16">
-        <v>7.401652464</v>
+        <v>7.36462764</v>
       </c>
       <c r="Q16">
-        <v>8.101652463999999</v>
+        <v>8.064627639999999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1163821291753215</v>
+        <v>0.1170655678504638</v>
       </c>
       <c r="T16">
-        <v>1.375777072074964</v>
+        <v>1.389098563937225</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>15.27932410196699</v>
+        <v>14.26070249516919</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2773,22 +2773,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1055417326728942</v>
+        <v>0.105361234255012</v>
       </c>
       <c r="C17">
-        <v>80.53586843995745</v>
+        <v>79.78483657297244</v>
       </c>
       <c r="D17">
-        <v>79.63736843995746</v>
+        <v>79.80643657297243</v>
       </c>
       <c r="E17">
-        <v>12.3915</v>
+        <v>13.3116</v>
       </c>
       <c r="F17">
-        <v>13.8015</v>
+        <v>14.7216</v>
       </c>
       <c r="G17">
         <v>14.7</v>
@@ -2809,28 +2809,28 @@
         <v>9.9</v>
       </c>
       <c r="M17">
-        <v>0.69421545</v>
+        <v>0.7404964799999999</v>
       </c>
       <c r="N17">
-        <v>9.205784550000001</v>
+        <v>9.159503520000001</v>
       </c>
       <c r="O17">
-        <v>1.84115691</v>
+        <v>1.831900704</v>
       </c>
       <c r="P17">
-        <v>7.36462764</v>
+        <v>7.327602816000001</v>
       </c>
       <c r="Q17">
-        <v>8.064627639999999</v>
+        <v>8.027602816</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1170655678504638</v>
+        <v>0.1177652788750143</v>
       </c>
       <c r="T17">
-        <v>1.389098563937225</v>
+        <v>1.402737234177158</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>14.26070249516919</v>
+        <v>13.36940858922112</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2855,22 +2855,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.105361234255012</v>
+        <v>0.1053847358371297</v>
       </c>
       <c r="C18">
-        <v>79.78483657297244</v>
+        <v>78.84268261994492</v>
       </c>
       <c r="D18">
-        <v>79.80643657297243</v>
+        <v>79.78438261994492</v>
       </c>
       <c r="E18">
-        <v>13.3116</v>
+        <v>14.2317</v>
       </c>
       <c r="F18">
-        <v>14.7216</v>
+        <v>15.6417</v>
       </c>
       <c r="G18">
         <v>14.7</v>
@@ -2891,45 +2891,45 @@
         <v>9.9</v>
       </c>
       <c r="M18">
-        <v>0.7404964799999999</v>
+        <v>0.81024006</v>
       </c>
       <c r="N18">
-        <v>9.159503520000001</v>
+        <v>9.08975994</v>
       </c>
       <c r="O18">
-        <v>1.831900704</v>
+        <v>1.817951988</v>
       </c>
       <c r="P18">
-        <v>7.327602816000001</v>
+        <v>7.271807952000001</v>
       </c>
       <c r="Q18">
-        <v>8.027602816</v>
+        <v>7.971807952</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1177652788750143</v>
+        <v>0.1184818504061804</v>
       </c>
       <c r="T18">
-        <v>1.402737234177158</v>
+        <v>1.416704547073475</v>
       </c>
       <c r="U18">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V18">
         <v>0.2</v>
       </c>
       <c r="W18">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y18">
-        <v>13.36940858922112</v>
+        <v>12.21860099092114</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2937,22 +2937,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1053847358371297</v>
+        <v>0.1052162374192475</v>
       </c>
       <c r="C19">
-        <v>78.84268261994492</v>
+        <v>78.08097214527449</v>
       </c>
       <c r="D19">
-        <v>79.78438261994492</v>
+        <v>79.94277214527449</v>
       </c>
       <c r="E19">
-        <v>14.2317</v>
+        <v>15.1518</v>
       </c>
       <c r="F19">
-        <v>15.6417</v>
+        <v>16.5618</v>
       </c>
       <c r="G19">
         <v>14.7</v>
@@ -2973,28 +2973,28 @@
         <v>9.9</v>
       </c>
       <c r="M19">
-        <v>0.81024006</v>
+        <v>0.8579012400000001</v>
       </c>
       <c r="N19">
-        <v>9.08975994</v>
+        <v>9.04209876</v>
       </c>
       <c r="O19">
-        <v>1.817951988</v>
+        <v>1.808419752</v>
       </c>
       <c r="P19">
-        <v>7.271807952000001</v>
+        <v>7.233679008</v>
       </c>
       <c r="Q19">
-        <v>7.971807952</v>
+        <v>7.933679007999999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1184818504061804</v>
+        <v>0.1192158992917652</v>
       </c>
       <c r="T19">
-        <v>1.416704547073475</v>
+        <v>1.431012526137996</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>12.21860099092114</v>
+        <v>11.53978982475885</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3019,22 +3019,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1052162374192475</v>
+        <v>0.1050477390013652</v>
       </c>
       <c r="C20">
-        <v>78.08097214527447</v>
+        <v>77.31989179754524</v>
       </c>
       <c r="D20">
-        <v>79.94277214527447</v>
+        <v>80.10179179754523</v>
       </c>
       <c r="E20">
-        <v>15.1518</v>
+        <v>16.0719</v>
       </c>
       <c r="F20">
-        <v>16.5618</v>
+        <v>17.4819</v>
       </c>
       <c r="G20">
         <v>14.7</v>
@@ -3055,28 +3055,28 @@
         <v>9.9</v>
       </c>
       <c r="M20">
-        <v>0.8579012399999999</v>
+        <v>0.90556242</v>
       </c>
       <c r="N20">
-        <v>9.04209876</v>
+        <v>8.99443758</v>
       </c>
       <c r="O20">
-        <v>1.808419752</v>
+        <v>1.798887516</v>
       </c>
       <c r="P20">
-        <v>7.233679008</v>
+        <v>7.195550064</v>
       </c>
       <c r="Q20">
-        <v>7.933679007999999</v>
+        <v>7.895550063999999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1192158992917652</v>
+        <v>0.1199680728411916</v>
       </c>
       <c r="T20">
-        <v>1.431012526137996</v>
+        <v>1.445673788636208</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.53978982475885</v>
+        <v>10.93243246556102</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3101,22 +3101,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1050477390013652</v>
+        <v>0.104879240583483</v>
       </c>
       <c r="C21">
-        <v>77.31989179754524</v>
+        <v>76.55944534453809</v>
       </c>
       <c r="D21">
-        <v>80.10179179754523</v>
+        <v>80.26144534453809</v>
       </c>
       <c r="E21">
-        <v>16.0719</v>
+        <v>16.992</v>
       </c>
       <c r="F21">
-        <v>17.4819</v>
+        <v>18.402</v>
       </c>
       <c r="G21">
         <v>14.7</v>
@@ -3137,28 +3137,28 @@
         <v>9.9</v>
       </c>
       <c r="M21">
-        <v>0.90556242</v>
+        <v>0.9532235999999998</v>
       </c>
       <c r="N21">
-        <v>8.99443758</v>
+        <v>8.946776400000001</v>
       </c>
       <c r="O21">
-        <v>1.798887516</v>
+        <v>1.78935528</v>
       </c>
       <c r="P21">
-        <v>7.195550064</v>
+        <v>7.15742112</v>
       </c>
       <c r="Q21">
-        <v>7.895550063999999</v>
+        <v>7.85742112</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1199680728411916</v>
+        <v>0.1207390507293537</v>
       </c>
       <c r="T21">
-        <v>1.445673788636208</v>
+        <v>1.460701582696875</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>10.93243246556102</v>
+        <v>10.38581084228297</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3183,22 +3183,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.104879240583483</v>
+        <v>0.1047107421656007</v>
       </c>
       <c r="C22">
-        <v>76.55944534453809</v>
+        <v>75.79963658413277</v>
       </c>
       <c r="D22">
-        <v>80.26144534453809</v>
+        <v>80.42173658413277</v>
       </c>
       <c r="E22">
-        <v>16.992</v>
+        <v>17.9121</v>
       </c>
       <c r="F22">
-        <v>18.402</v>
+        <v>19.3221</v>
       </c>
       <c r="G22">
         <v>14.7</v>
@@ -3219,28 +3219,28 @@
         <v>9.9</v>
       </c>
       <c r="M22">
-        <v>0.9532235999999998</v>
+        <v>1.00088478</v>
       </c>
       <c r="N22">
-        <v>8.946776400000001</v>
+        <v>8.899115220000001</v>
       </c>
       <c r="O22">
-        <v>1.78935528</v>
+        <v>1.779823044</v>
       </c>
       <c r="P22">
-        <v>7.15742112</v>
+        <v>7.119292176</v>
       </c>
       <c r="Q22">
-        <v>7.85742112</v>
+        <v>7.819292175999999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1207390507293537</v>
+        <v>0.1215295470450642</v>
       </c>
       <c r="T22">
-        <v>1.460701582696875</v>
+        <v>1.476109827240091</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.38581084228297</v>
+        <v>9.891248421221871</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3265,22 +3265,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1047107421656007</v>
+        <v>0.1048414437477184</v>
       </c>
       <c r="C23">
-        <v>75.79963658413277</v>
+        <v>74.75514556748561</v>
       </c>
       <c r="D23">
-        <v>80.42173658413277</v>
+        <v>80.29734556748561</v>
       </c>
       <c r="E23">
-        <v>17.9121</v>
+        <v>18.8322</v>
       </c>
       <c r="F23">
-        <v>19.3221</v>
+        <v>20.2422</v>
       </c>
       <c r="G23">
         <v>14.7</v>
@@ -3301,45 +3301,45 @@
         <v>9.9</v>
       </c>
       <c r="M23">
-        <v>1.00088478</v>
+        <v>1.0829577</v>
       </c>
       <c r="N23">
-        <v>8.899115220000001</v>
+        <v>8.817042300000001</v>
       </c>
       <c r="O23">
-        <v>1.779823044</v>
+        <v>1.76340846</v>
       </c>
       <c r="P23">
-        <v>7.119292176</v>
+        <v>7.053633840000001</v>
       </c>
       <c r="Q23">
-        <v>7.819292175999999</v>
+        <v>7.75363384</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1215295470450642</v>
+        <v>0.1223403124970749</v>
       </c>
       <c r="T23">
-        <v>1.476109827240091</v>
+        <v>1.491913154976723</v>
       </c>
       <c r="U23">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V23">
         <v>0.2</v>
       </c>
       <c r="W23">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>9.891248421221871</v>
+        <v>9.141631293632246</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3347,22 +3347,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1048414437477184</v>
+        <v>0.1046865453298362</v>
       </c>
       <c r="C24">
-        <v>74.75514556748561</v>
+        <v>73.9825074331475</v>
       </c>
       <c r="D24">
-        <v>80.29734556748561</v>
+        <v>80.4448074331475</v>
       </c>
       <c r="E24">
-        <v>18.8322</v>
+        <v>19.7523</v>
       </c>
       <c r="F24">
-        <v>20.2422</v>
+        <v>21.1623</v>
       </c>
       <c r="G24">
         <v>14.7</v>
@@ -3383,28 +3383,28 @@
         <v>9.9</v>
       </c>
       <c r="M24">
-        <v>1.0829577</v>
+        <v>1.13218305</v>
       </c>
       <c r="N24">
-        <v>8.817042300000001</v>
+        <v>8.76781695</v>
       </c>
       <c r="O24">
-        <v>1.76340846</v>
+        <v>1.75356339</v>
       </c>
       <c r="P24">
-        <v>7.053633840000001</v>
+        <v>7.01425356</v>
       </c>
       <c r="Q24">
-        <v>7.75363384</v>
+        <v>7.71425356</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1223403124970749</v>
+        <v>0.123172136791995</v>
       </c>
       <c r="T24">
-        <v>1.491913154976723</v>
+        <v>1.508126958758462</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>9.141631293632246</v>
+        <v>8.744169063474322</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3429,22 +3429,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1046865453298362</v>
+        <v>0.1045316469119539</v>
       </c>
       <c r="C25">
-        <v>73.9825074331475</v>
+        <v>73.21041190725296</v>
       </c>
       <c r="D25">
-        <v>80.4448074331475</v>
+        <v>80.59281190725295</v>
       </c>
       <c r="E25">
-        <v>19.7523</v>
+        <v>20.6724</v>
       </c>
       <c r="F25">
-        <v>21.1623</v>
+        <v>22.0824</v>
       </c>
       <c r="G25">
         <v>14.7</v>
@@ -3465,28 +3465,28 @@
         <v>9.9</v>
       </c>
       <c r="M25">
-        <v>1.13218305</v>
+        <v>1.1814084</v>
       </c>
       <c r="N25">
-        <v>8.76781695</v>
+        <v>8.7185916</v>
       </c>
       <c r="O25">
-        <v>1.75356339</v>
+        <v>1.74371832</v>
       </c>
       <c r="P25">
-        <v>7.01425356</v>
+        <v>6.97487328</v>
       </c>
       <c r="Q25">
-        <v>7.71425356</v>
+        <v>7.674873279999999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.123172136791995</v>
+        <v>0.1240258511999394</v>
       </c>
       <c r="T25">
-        <v>1.508126958758462</v>
+        <v>1.524767441587089</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.744169063474322</v>
+        <v>8.379828685829558</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1045316469119539</v>
+        <v>0.1043767484940717</v>
       </c>
       <c r="C26">
-        <v>73.21041190725296</v>
+        <v>72.43886199023818</v>
       </c>
       <c r="D26">
-        <v>80.59281190725295</v>
+        <v>80.74136199023818</v>
       </c>
       <c r="E26">
-        <v>20.6724</v>
+        <v>21.5925</v>
       </c>
       <c r="F26">
-        <v>22.0824</v>
+        <v>23.0025</v>
       </c>
       <c r="G26">
         <v>14.7</v>
@@ -3547,28 +3547,28 @@
         <v>9.9</v>
       </c>
       <c r="M26">
-        <v>1.1814084</v>
+        <v>1.23063375</v>
       </c>
       <c r="N26">
-        <v>8.7185916</v>
+        <v>8.669366250000001</v>
       </c>
       <c r="O26">
-        <v>1.74371832</v>
+        <v>1.73387325</v>
       </c>
       <c r="P26">
-        <v>6.97487328</v>
+        <v>6.935493000000001</v>
       </c>
       <c r="Q26">
-        <v>7.674873279999999</v>
+        <v>7.635493</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1240258511999394</v>
+        <v>0.1249023313254289</v>
       </c>
       <c r="T26">
-        <v>1.524767441587089</v>
+        <v>1.541851670624479</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.379828685829558</v>
+        <v>8.044635538396378</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3593,22 +3593,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1043767484940717</v>
+        <v>0.1042218500761894</v>
       </c>
       <c r="C27">
-        <v>72.43886199023818</v>
+        <v>71.66786070470197</v>
       </c>
       <c r="D27">
-        <v>80.74136199023818</v>
+        <v>80.89046070470197</v>
       </c>
       <c r="E27">
-        <v>21.5925</v>
+        <v>22.5126</v>
       </c>
       <c r="F27">
-        <v>23.0025</v>
+        <v>23.9226</v>
       </c>
       <c r="G27">
         <v>14.7</v>
@@ -3629,28 +3629,28 @@
         <v>9.9</v>
       </c>
       <c r="M27">
-        <v>1.23063375</v>
+        <v>1.2798591</v>
       </c>
       <c r="N27">
-        <v>8.669366250000001</v>
+        <v>8.620140900000001</v>
       </c>
       <c r="O27">
-        <v>1.73387325</v>
+        <v>1.72402818</v>
       </c>
       <c r="P27">
-        <v>6.935493000000001</v>
+        <v>6.896112720000001</v>
       </c>
       <c r="Q27">
-        <v>7.635493</v>
+        <v>7.59611272</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1249023313254289</v>
+        <v>0.1258025001029587</v>
       </c>
       <c r="T27">
-        <v>1.541851670624479</v>
+        <v>1.559397635581799</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.044635538396378</v>
+        <v>7.735226479227284</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3675,22 +3675,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1042218500761894</v>
+        <v>0.1042397516583072</v>
       </c>
       <c r="C28">
-        <v>71.66786070470197</v>
+        <v>70.73050125695505</v>
       </c>
       <c r="D28">
-        <v>80.89046070470197</v>
+        <v>80.87320125695504</v>
       </c>
       <c r="E28">
-        <v>22.5126</v>
+        <v>23.4327</v>
       </c>
       <c r="F28">
-        <v>23.9226</v>
+        <v>24.8427</v>
       </c>
       <c r="G28">
         <v>14.7</v>
@@ -3711,45 +3711,45 @@
         <v>9.9</v>
       </c>
       <c r="M28">
-        <v>1.2798591</v>
+        <v>1.34895861</v>
       </c>
       <c r="N28">
-        <v>8.620140900000001</v>
+        <v>8.55104139</v>
       </c>
       <c r="O28">
-        <v>1.72402818</v>
+        <v>1.710208278</v>
       </c>
       <c r="P28">
-        <v>6.896112720000001</v>
+        <v>6.840833112</v>
       </c>
       <c r="Q28">
-        <v>7.59611272</v>
+        <v>7.540833112</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1258025001029587</v>
+        <v>0.126727331038777</v>
       </c>
       <c r="T28">
-        <v>1.559397635581799</v>
+        <v>1.577424311907813</v>
       </c>
       <c r="U28">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V28">
         <v>0.2</v>
       </c>
       <c r="W28">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y28">
-        <v>7.735226479227284</v>
+        <v>7.338994633793841</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3757,22 +3757,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1042397516583072</v>
+        <v>0.1040912532404249</v>
       </c>
       <c r="C29">
-        <v>70.73050125695505</v>
+        <v>69.95379625135841</v>
       </c>
       <c r="D29">
-        <v>80.87320125695504</v>
+        <v>81.01659625135841</v>
       </c>
       <c r="E29">
-        <v>23.4327</v>
+        <v>24.3528</v>
       </c>
       <c r="F29">
-        <v>24.8427</v>
+        <v>25.7628</v>
       </c>
       <c r="G29">
         <v>14.7</v>
@@ -3793,28 +3793,28 @@
         <v>9.9</v>
       </c>
       <c r="M29">
-        <v>1.34895861</v>
+        <v>1.39892004</v>
       </c>
       <c r="N29">
-        <v>8.55104139</v>
+        <v>8.50107996</v>
       </c>
       <c r="O29">
-        <v>1.710208278</v>
+        <v>1.700215992</v>
       </c>
       <c r="P29">
-        <v>6.840833112</v>
+        <v>6.800863968</v>
       </c>
       <c r="Q29">
-        <v>7.540833112</v>
+        <v>7.500863967999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.126727331038777</v>
+        <v>0.1276778517228124</v>
       </c>
       <c r="T29">
-        <v>1.577424311907813</v>
+        <v>1.595951729242882</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.338994633793841</v>
+        <v>7.07688768258692</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3839,22 +3839,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1040912532404249</v>
+        <v>0.1039427548225427</v>
       </c>
       <c r="C30">
-        <v>69.95379625135841</v>
+        <v>69.17760065177603</v>
       </c>
       <c r="D30">
-        <v>81.01659625135841</v>
+        <v>81.16050065177603</v>
       </c>
       <c r="E30">
-        <v>24.3528</v>
+        <v>25.2729</v>
       </c>
       <c r="F30">
-        <v>25.7628</v>
+        <v>26.6829</v>
       </c>
       <c r="G30">
         <v>14.7</v>
@@ -3875,28 +3875,28 @@
         <v>9.9</v>
       </c>
       <c r="M30">
-        <v>1.39892004</v>
+        <v>1.44888147</v>
       </c>
       <c r="N30">
-        <v>8.50107996</v>
+        <v>8.45111853</v>
       </c>
       <c r="O30">
-        <v>1.700215992</v>
+        <v>1.690223706</v>
       </c>
       <c r="P30">
-        <v>6.800863968</v>
+        <v>6.760894824</v>
       </c>
       <c r="Q30">
-        <v>7.500863967999999</v>
+        <v>7.460894823999999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1276778517228124</v>
+        <v>0.128655147637384</v>
       </c>
       <c r="T30">
-        <v>1.595951729242882</v>
+        <v>1.615001045657813</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.07688768258692</v>
+        <v>6.832857072842542</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3921,22 +3921,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1039427548225427</v>
+        <v>0.1037942564046604</v>
       </c>
       <c r="C31">
-        <v>69.17760065177603</v>
+        <v>68.40191717751027</v>
       </c>
       <c r="D31">
-        <v>81.16050065177603</v>
+        <v>81.30491717751026</v>
       </c>
       <c r="E31">
-        <v>25.2729</v>
+        <v>26.193</v>
       </c>
       <c r="F31">
-        <v>26.6829</v>
+        <v>27.603</v>
       </c>
       <c r="G31">
         <v>14.7</v>
@@ -3957,28 +3957,28 @@
         <v>9.9</v>
       </c>
       <c r="M31">
-        <v>1.44888147</v>
+        <v>1.4988429</v>
       </c>
       <c r="N31">
-        <v>8.45111853</v>
+        <v>8.401157100000001</v>
       </c>
       <c r="O31">
-        <v>1.690223706</v>
+        <v>1.68023142</v>
       </c>
       <c r="P31">
-        <v>6.760894824</v>
+        <v>6.720925680000001</v>
       </c>
       <c r="Q31">
-        <v>7.460894823999999</v>
+        <v>7.42092568</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.128655147637384</v>
+        <v>0.129660366292372</v>
       </c>
       <c r="T31">
-        <v>1.615001045657813</v>
+        <v>1.634594628256027</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.832857072842543</v>
+        <v>6.605095170414459</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4003,22 +4003,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1037942564046604</v>
+        <v>0.1036457579867781</v>
       </c>
       <c r="C32">
-        <v>68.40191717751027</v>
+        <v>67.6267485672528</v>
       </c>
       <c r="D32">
-        <v>81.30491717751026</v>
+        <v>81.4498485672528</v>
       </c>
       <c r="E32">
-        <v>26.193</v>
+        <v>27.1131</v>
       </c>
       <c r="F32">
-        <v>27.603</v>
+        <v>28.5231</v>
       </c>
       <c r="G32">
         <v>14.7</v>
@@ -4039,28 +4039,28 @@
         <v>9.9</v>
       </c>
       <c r="M32">
-        <v>1.4988429</v>
+        <v>1.54880433</v>
       </c>
       <c r="N32">
-        <v>8.401157100000001</v>
+        <v>8.351195670000001</v>
       </c>
       <c r="O32">
-        <v>1.68023142</v>
+        <v>1.670239134</v>
       </c>
       <c r="P32">
-        <v>6.720925680000001</v>
+        <v>6.680956536000001</v>
       </c>
       <c r="Q32">
-        <v>7.42092568</v>
+        <v>7.380956536</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.129660366292372</v>
+        <v>0.1306947217199683</v>
       </c>
       <c r="T32">
-        <v>1.634594628256027</v>
+        <v>1.654756140784625</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -4077,7 +4077,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.605095170414459</v>
+        <v>6.392027584272057</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4085,22 +4085,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1036457579867781</v>
+        <v>0.1034972595688959</v>
       </c>
       <c r="C33">
-        <v>67.6267485672528</v>
+        <v>66.85209757925782</v>
       </c>
       <c r="D33">
-        <v>81.4498485672528</v>
+        <v>81.5952975792578</v>
       </c>
       <c r="E33">
-        <v>27.1131</v>
+        <v>28.0332</v>
       </c>
       <c r="F33">
-        <v>28.5231</v>
+        <v>29.4432</v>
       </c>
       <c r="G33">
         <v>14.7</v>
@@ -4121,28 +4121,28 @@
         <v>9.9</v>
       </c>
       <c r="M33">
-        <v>1.54880433</v>
+        <v>1.59876576</v>
       </c>
       <c r="N33">
-        <v>8.351195670000001</v>
+        <v>8.301234240000001</v>
       </c>
       <c r="O33">
-        <v>1.670239134</v>
+        <v>1.660246848</v>
       </c>
       <c r="P33">
-        <v>6.680956536000001</v>
+        <v>6.640987392000001</v>
       </c>
       <c r="Q33">
-        <v>7.380956536</v>
+        <v>7.340987392000001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1306947217199683</v>
+        <v>0.1317594993660234</v>
       </c>
       <c r="T33">
-        <v>1.654756140784625</v>
+        <v>1.675510638975828</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.392027584272057</v>
+        <v>6.192276722263555</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4167,22 +4167,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1034972595688959</v>
+        <v>0.1036127611510136</v>
       </c>
       <c r="C34">
-        <v>66.85209757925782</v>
+        <v>65.81882298746969</v>
       </c>
       <c r="D34">
-        <v>81.5952975792578</v>
+        <v>81.48212298746968</v>
       </c>
       <c r="E34">
-        <v>28.0332</v>
+        <v>28.9533</v>
       </c>
       <c r="F34">
-        <v>29.4432</v>
+        <v>30.3633</v>
       </c>
       <c r="G34">
         <v>14.7</v>
@@ -4203,45 +4203,45 @@
         <v>9.9</v>
       </c>
       <c r="M34">
-        <v>1.59876576</v>
+        <v>1.67909049</v>
       </c>
       <c r="N34">
-        <v>8.301234240000001</v>
+        <v>8.22090951</v>
       </c>
       <c r="O34">
-        <v>1.660246848</v>
+        <v>1.644181902</v>
       </c>
       <c r="P34">
-        <v>6.640987392000001</v>
+        <v>6.576727608000001</v>
       </c>
       <c r="Q34">
-        <v>7.340987392000001</v>
+        <v>7.276727608</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1317594993660234</v>
+        <v>0.1328560614194233</v>
       </c>
       <c r="T34">
-        <v>1.675510638975828</v>
+        <v>1.69688467442647</v>
       </c>
       <c r="U34">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V34">
         <v>0.2</v>
       </c>
       <c r="W34">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y34">
-        <v>6.192276722263555</v>
+        <v>5.89604911644756</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4249,22 +4249,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1036127611510136</v>
+        <v>0.1034722627331314</v>
       </c>
       <c r="C35">
-        <v>65.81882298746969</v>
+        <v>65.03643220299809</v>
       </c>
       <c r="D35">
-        <v>81.48212298746968</v>
+        <v>81.61983220299808</v>
       </c>
       <c r="E35">
-        <v>28.9533</v>
+        <v>29.8734</v>
       </c>
       <c r="F35">
-        <v>30.3633</v>
+        <v>31.2834</v>
       </c>
       <c r="G35">
         <v>14.7</v>
@@ -4285,28 +4285,28 @@
         <v>9.9</v>
       </c>
       <c r="M35">
-        <v>1.67909049</v>
+        <v>1.72997202</v>
       </c>
       <c r="N35">
-        <v>8.22090951</v>
+        <v>8.17002798</v>
       </c>
       <c r="O35">
-        <v>1.644181902</v>
+        <v>1.634005596</v>
       </c>
       <c r="P35">
-        <v>6.576727608000001</v>
+        <v>6.536022384000001</v>
       </c>
       <c r="Q35">
-        <v>7.276727608</v>
+        <v>7.236022384</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1328560614194233</v>
+        <v>0.1339858526259566</v>
       </c>
       <c r="T35">
-        <v>1.69688467442647</v>
+        <v>1.718906407921071</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.89604911644756</v>
+        <v>5.722635907140278</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4331,22 +4331,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1034722627331314</v>
+        <v>0.1033317643152491</v>
       </c>
       <c r="C36">
-        <v>65.03643220299809</v>
+        <v>64.25450767864595</v>
       </c>
       <c r="D36">
-        <v>81.61983220299808</v>
+        <v>81.75800767864594</v>
       </c>
       <c r="E36">
-        <v>29.8734</v>
+        <v>30.7935</v>
       </c>
       <c r="F36">
-        <v>31.2834</v>
+        <v>32.2035</v>
       </c>
       <c r="G36">
         <v>14.7</v>
@@ -4367,28 +4367,28 @@
         <v>9.9</v>
       </c>
       <c r="M36">
-        <v>1.72997202</v>
+        <v>1.78085355</v>
       </c>
       <c r="N36">
-        <v>8.17002798</v>
+        <v>8.119146450000001</v>
       </c>
       <c r="O36">
-        <v>1.634005596</v>
+        <v>1.62382929</v>
       </c>
       <c r="P36">
-        <v>6.536022384000001</v>
+        <v>6.495317160000001</v>
       </c>
       <c r="Q36">
-        <v>7.236022384</v>
+        <v>7.19531716</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1339858526259566</v>
+        <v>0.1351504066388448</v>
       </c>
       <c r="T36">
-        <v>1.718906407921071</v>
+        <v>1.741605733215505</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.722635907140278</v>
+        <v>5.559132024079128</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4413,22 +4413,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1033317643152491</v>
+        <v>0.1031912658973669</v>
       </c>
       <c r="C37">
-        <v>64.25450767864595</v>
+        <v>63.4730517864458</v>
       </c>
       <c r="D37">
-        <v>81.75800767864594</v>
+        <v>81.8966517864458</v>
       </c>
       <c r="E37">
-        <v>30.7935</v>
+        <v>31.7136</v>
       </c>
       <c r="F37">
-        <v>32.2035</v>
+        <v>33.1236</v>
       </c>
       <c r="G37">
         <v>14.7</v>
@@ -4449,28 +4449,28 @@
         <v>9.9</v>
       </c>
       <c r="M37">
-        <v>1.78085355</v>
+        <v>1.83173508</v>
       </c>
       <c r="N37">
-        <v>8.119146450000001</v>
+        <v>8.068264920000001</v>
       </c>
       <c r="O37">
-        <v>1.62382929</v>
+        <v>1.613652984</v>
       </c>
       <c r="P37">
-        <v>6.495317160000001</v>
+        <v>6.454611936000001</v>
       </c>
       <c r="Q37">
-        <v>7.19531716</v>
+        <v>7.154611936</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1351504066388448</v>
+        <v>0.1363513529646357</v>
       </c>
       <c r="T37">
-        <v>1.741605733215505</v>
+        <v>1.765014412425391</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4487,7 +4487,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.559132024079128</v>
+        <v>5.40471169007693</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4495,22 +4495,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1031912658973669</v>
+        <v>0.1030507674794846</v>
       </c>
       <c r="C38">
-        <v>63.47305178644581</v>
+        <v>62.69206691454739</v>
       </c>
       <c r="D38">
-        <v>81.8966517864458</v>
+        <v>82.03576691454738</v>
       </c>
       <c r="E38">
-        <v>31.7136</v>
+        <v>32.6337</v>
       </c>
       <c r="F38">
-        <v>33.1236</v>
+        <v>34.04369999999999</v>
       </c>
       <c r="G38">
         <v>14.7</v>
@@ -4531,28 +4531,28 @@
         <v>9.9</v>
       </c>
       <c r="M38">
-        <v>1.83173508</v>
+        <v>1.88261661</v>
       </c>
       <c r="N38">
-        <v>8.068264920000001</v>
+        <v>8.017383390000001</v>
       </c>
       <c r="O38">
-        <v>1.613652984</v>
+        <v>1.603476678</v>
       </c>
       <c r="P38">
-        <v>6.454611936000001</v>
+        <v>6.413906712000001</v>
       </c>
       <c r="Q38">
-        <v>7.154611936</v>
+        <v>7.113906712</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1363513529646357</v>
+        <v>0.1375904245706105</v>
       </c>
       <c r="T38">
-        <v>1.765014412425391</v>
+        <v>1.789166224308607</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4569,7 +4569,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.404711690076931</v>
+        <v>5.258638401155933</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1030507674794846</v>
+        <v>0.1029102690616023</v>
       </c>
       <c r="C39">
-        <v>62.69206691454739</v>
+        <v>61.91155546735468</v>
       </c>
       <c r="D39">
-        <v>82.03576691454738</v>
+        <v>82.17535546735468</v>
       </c>
       <c r="E39">
-        <v>32.6337</v>
+        <v>33.5538</v>
       </c>
       <c r="F39">
-        <v>34.04369999999999</v>
+        <v>34.9638</v>
       </c>
       <c r="G39">
         <v>14.7</v>
@@ -4613,28 +4613,28 @@
         <v>9.9</v>
       </c>
       <c r="M39">
-        <v>1.88261661</v>
+        <v>1.93349814</v>
       </c>
       <c r="N39">
-        <v>8.017383390000001</v>
+        <v>7.96650186</v>
       </c>
       <c r="O39">
-        <v>1.603476678</v>
+        <v>1.593300372</v>
       </c>
       <c r="P39">
-        <v>6.413906712000001</v>
+        <v>6.373201488</v>
       </c>
       <c r="Q39">
-        <v>7.113906712</v>
+        <v>7.073201488</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1375904245706105</v>
+        <v>0.1388694662283909</v>
       </c>
       <c r="T39">
-        <v>1.789166224308607</v>
+        <v>1.814097126897732</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.258638401155933</v>
+        <v>5.120253180072881</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4659,22 +4659,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1029102690616023</v>
+        <v>0.1027697706437201</v>
       </c>
       <c r="C40">
-        <v>61.91155546735468</v>
+        <v>61.13151986566452</v>
       </c>
       <c r="D40">
-        <v>82.17535546735468</v>
+        <v>82.31541986566451</v>
       </c>
       <c r="E40">
-        <v>33.5538</v>
+        <v>34.4739</v>
       </c>
       <c r="F40">
-        <v>34.9638</v>
+        <v>35.8839</v>
       </c>
       <c r="G40">
         <v>14.7</v>
@@ -4695,28 +4695,28 @@
         <v>9.9</v>
       </c>
       <c r="M40">
-        <v>1.93349814</v>
+        <v>1.98437967</v>
       </c>
       <c r="N40">
-        <v>7.96650186</v>
+        <v>7.91562033</v>
       </c>
       <c r="O40">
-        <v>1.593300372</v>
+        <v>1.583124066</v>
       </c>
       <c r="P40">
-        <v>6.373201488</v>
+        <v>6.332496264</v>
       </c>
       <c r="Q40">
-        <v>7.073201488</v>
+        <v>7.032496264</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1388694662283909</v>
+        <v>0.1401904436782297</v>
       </c>
       <c r="T40">
-        <v>1.814097126897732</v>
+        <v>1.839845436129125</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.120253180072881</v>
+        <v>4.98896463699409</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4741,22 +4741,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1027697706437201</v>
+        <v>0.1026292722258378</v>
       </c>
       <c r="C41">
-        <v>61.13151986566452</v>
+        <v>60.35196254680653</v>
       </c>
       <c r="D41">
-        <v>82.31541986566451</v>
+        <v>82.45596254680652</v>
       </c>
       <c r="E41">
-        <v>34.4739</v>
+        <v>35.394</v>
       </c>
       <c r="F41">
-        <v>35.8839</v>
+        <v>36.80399999999999</v>
       </c>
       <c r="G41">
         <v>14.7</v>
@@ -4777,28 +4777,28 @@
         <v>9.9</v>
       </c>
       <c r="M41">
-        <v>1.98437967</v>
+        <v>2.0352612</v>
       </c>
       <c r="N41">
-        <v>7.91562033</v>
+        <v>7.8647388</v>
       </c>
       <c r="O41">
-        <v>1.583124066</v>
+        <v>1.57294776</v>
       </c>
       <c r="P41">
-        <v>6.332496264</v>
+        <v>6.291791040000001</v>
       </c>
       <c r="Q41">
-        <v>7.032496264</v>
+        <v>6.99179104</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1401904436782297</v>
+        <v>0.1415554537097297</v>
       </c>
       <c r="T41">
-        <v>1.839845436129125</v>
+        <v>1.866452022334896</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.98896463699409</v>
+        <v>4.864240521069237</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4823,22 +4823,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1026292722258378</v>
+        <v>0.1024887738079556</v>
       </c>
       <c r="C42">
-        <v>60.35196254680653</v>
+        <v>59.57288596478437</v>
       </c>
       <c r="D42">
-        <v>82.45596254680652</v>
+        <v>82.59698596478437</v>
       </c>
       <c r="E42">
-        <v>35.394</v>
+        <v>36.3141</v>
       </c>
       <c r="F42">
-        <v>36.80399999999999</v>
+        <v>37.7241</v>
       </c>
       <c r="G42">
         <v>14.7</v>
@@ -4859,28 +4859,28 @@
         <v>9.9</v>
       </c>
       <c r="M42">
-        <v>2.0352612</v>
+        <v>2.08614273</v>
       </c>
       <c r="N42">
-        <v>7.8647388</v>
+        <v>7.81385727</v>
       </c>
       <c r="O42">
-        <v>1.57294776</v>
+        <v>1.562771454</v>
       </c>
       <c r="P42">
-        <v>6.291791040000001</v>
+        <v>6.251085816</v>
       </c>
       <c r="Q42">
-        <v>6.99179104</v>
+        <v>6.951085815999999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1415554537097297</v>
+        <v>0.1429667352677213</v>
       </c>
       <c r="T42">
-        <v>1.866452022334896</v>
+        <v>1.893960526717135</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.864240521069237</v>
+        <v>4.74560050836023</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4905,22 +4905,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1024887738079556</v>
+        <v>0.1023482753900733</v>
       </c>
       <c r="C43">
-        <v>59.57288596478437</v>
+        <v>58.79429259041879</v>
       </c>
       <c r="D43">
-        <v>82.59698596478437</v>
+        <v>82.73849259041879</v>
       </c>
       <c r="E43">
-        <v>36.3141</v>
+        <v>37.2342</v>
       </c>
       <c r="F43">
-        <v>37.7241</v>
+        <v>38.6442</v>
       </c>
       <c r="G43">
         <v>14.7</v>
@@ -4941,28 +4941,28 @@
         <v>9.9</v>
       </c>
       <c r="M43">
-        <v>2.08614273</v>
+        <v>2.13702426</v>
       </c>
       <c r="N43">
-        <v>7.81385727</v>
+        <v>7.76297574</v>
       </c>
       <c r="O43">
-        <v>1.562771454</v>
+        <v>1.552595148</v>
       </c>
       <c r="P43">
-        <v>6.251085816</v>
+        <v>6.210380592</v>
       </c>
       <c r="Q43">
-        <v>6.951085815999999</v>
+        <v>6.910380591999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1429667352677213</v>
+        <v>0.144426681707023</v>
       </c>
       <c r="T43">
-        <v>1.893960526717135</v>
+        <v>1.922417600216003</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.74560050836023</v>
+        <v>4.63261002006594</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4987,22 +4987,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1023482753900733</v>
+        <v>0.1022077769721911</v>
       </c>
       <c r="C44">
-        <v>58.79429259041879</v>
+        <v>58.0161849114917</v>
       </c>
       <c r="D44">
-        <v>82.73849259041879</v>
+        <v>82.88048491149169</v>
       </c>
       <c r="E44">
-        <v>37.2342</v>
+        <v>38.1543</v>
       </c>
       <c r="F44">
-        <v>38.6442</v>
+        <v>39.5643</v>
       </c>
       <c r="G44">
         <v>14.7</v>
@@ -5023,28 +5023,28 @@
         <v>9.9</v>
       </c>
       <c r="M44">
-        <v>2.13702426</v>
+        <v>2.18790579</v>
       </c>
       <c r="N44">
-        <v>7.76297574</v>
+        <v>7.71209421</v>
       </c>
       <c r="O44">
-        <v>1.552595148</v>
+        <v>1.542418842</v>
       </c>
       <c r="P44">
-        <v>6.210380592</v>
+        <v>6.169675368</v>
       </c>
       <c r="Q44">
-        <v>6.910380591999999</v>
+        <v>6.869675367999999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.144426681707023</v>
+        <v>0.1459378543371773</v>
       </c>
       <c r="T44">
-        <v>1.922417600216002</v>
+        <v>1.951873167521848</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.63261002006594</v>
+        <v>4.524874903320221</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5069,22 +5069,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1022077769721911</v>
+        <v>0.1029472785543088</v>
       </c>
       <c r="C45">
-        <v>58.0161849114917</v>
+        <v>56.35413958296685</v>
       </c>
       <c r="D45">
-        <v>82.88048491149169</v>
+        <v>82.13853958296684</v>
       </c>
       <c r="E45">
-        <v>38.1543</v>
+        <v>39.0744</v>
       </c>
       <c r="F45">
-        <v>39.5643</v>
+        <v>40.48439999999999</v>
       </c>
       <c r="G45">
         <v>14.7</v>
@@ -5105,45 +5105,45 @@
         <v>9.9</v>
       </c>
       <c r="M45">
-        <v>2.18790579</v>
+        <v>2.33999832</v>
       </c>
       <c r="N45">
-        <v>7.71209421</v>
+        <v>7.560001680000001</v>
       </c>
       <c r="O45">
-        <v>1.542418842</v>
+        <v>1.512000336</v>
       </c>
       <c r="P45">
-        <v>6.169675368</v>
+        <v>6.048001344000001</v>
       </c>
       <c r="Q45">
-        <v>6.869675367999999</v>
+        <v>6.748001344</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1459378543371773</v>
+        <v>0.1475029974184086</v>
       </c>
       <c r="T45">
-        <v>1.951873167521848</v>
+        <v>1.982380719374331</v>
       </c>
       <c r="U45">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V45">
         <v>0.2</v>
       </c>
       <c r="W45">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y45">
-        <v>4.524874903320221</v>
+        <v>4.230772268246757</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5151,22 +5151,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1029472785543088</v>
+        <v>0.1028267801364266</v>
       </c>
       <c r="C46">
-        <v>56.35413958296685</v>
+        <v>55.55402895967518</v>
       </c>
       <c r="D46">
-        <v>82.13853958296684</v>
+        <v>82.25852895967517</v>
       </c>
       <c r="E46">
-        <v>39.0744</v>
+        <v>39.9945</v>
       </c>
       <c r="F46">
-        <v>40.48439999999999</v>
+        <v>41.4045</v>
       </c>
       <c r="G46">
         <v>14.7</v>
@@ -5187,28 +5187,28 @@
         <v>9.9</v>
       </c>
       <c r="M46">
-        <v>2.33999832</v>
+        <v>2.3931801</v>
       </c>
       <c r="N46">
-        <v>7.560001680000001</v>
+        <v>7.5068199</v>
       </c>
       <c r="O46">
-        <v>1.512000336</v>
+        <v>1.50136398</v>
       </c>
       <c r="P46">
-        <v>6.048001344000001</v>
+        <v>6.00545592</v>
       </c>
       <c r="Q46">
-        <v>6.748001344</v>
+        <v>6.705455919999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1475029974184086</v>
+        <v>0.1491250547935028</v>
       </c>
       <c r="T46">
-        <v>1.982380719374331</v>
+        <v>2.013997636748722</v>
       </c>
       <c r="U46">
         <v>0.0578</v>
@@ -5225,7 +5225,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.230772268246757</v>
+        <v>4.136755106730162</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5233,22 +5233,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1028267801364266</v>
+        <v>0.1027062817185443</v>
       </c>
       <c r="C47">
-        <v>55.55402895967518</v>
+        <v>54.75426941429181</v>
       </c>
       <c r="D47">
-        <v>82.25852895967517</v>
+        <v>82.3788694142918</v>
       </c>
       <c r="E47">
-        <v>39.9945</v>
+        <v>40.9146</v>
       </c>
       <c r="F47">
-        <v>41.4045</v>
+        <v>42.3246</v>
       </c>
       <c r="G47">
         <v>14.7</v>
@@ -5269,28 +5269,28 @@
         <v>9.9</v>
       </c>
       <c r="M47">
-        <v>2.3931801</v>
+        <v>2.44636188</v>
       </c>
       <c r="N47">
-        <v>7.5068199</v>
+        <v>7.453638120000001</v>
       </c>
       <c r="O47">
-        <v>1.50136398</v>
+        <v>1.490727624</v>
       </c>
       <c r="P47">
-        <v>6.00545592</v>
+        <v>5.962910496000001</v>
       </c>
       <c r="Q47">
-        <v>6.705455919999999</v>
+        <v>6.662910496</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1491250547935028</v>
+        <v>0.1508071883676746</v>
       </c>
       <c r="T47">
-        <v>2.013997636748722</v>
+        <v>2.046785551062906</v>
       </c>
       <c r="U47">
         <v>0.0578</v>
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.136755106730162</v>
+        <v>4.046825647888202</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5315,22 +5315,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1027062817185443</v>
+        <v>0.103901783300662</v>
       </c>
       <c r="C48">
-        <v>54.75426941429181</v>
+        <v>52.65559468478362</v>
       </c>
       <c r="D48">
-        <v>82.3788694142918</v>
+        <v>81.20029468478361</v>
       </c>
       <c r="E48">
-        <v>40.9146</v>
+        <v>41.83470000000001</v>
       </c>
       <c r="F48">
-        <v>42.3246</v>
+        <v>43.2447</v>
       </c>
       <c r="G48">
         <v>14.7</v>
@@ -5351,45 +5351,45 @@
         <v>9.9</v>
       </c>
       <c r="M48">
-        <v>2.44636188</v>
+        <v>2.65090011</v>
       </c>
       <c r="N48">
-        <v>7.453638120000001</v>
+        <v>7.24909989</v>
       </c>
       <c r="O48">
-        <v>1.490727624</v>
+        <v>1.449819978</v>
       </c>
       <c r="P48">
-        <v>5.962910496000001</v>
+        <v>5.799279912</v>
       </c>
       <c r="Q48">
-        <v>6.662910496</v>
+        <v>6.499279912</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1508071883676746</v>
+        <v>0.1525527986804944</v>
       </c>
       <c r="T48">
-        <v>2.046785551062906</v>
+        <v>2.08081074516253</v>
       </c>
       <c r="U48">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V48">
         <v>0.2</v>
       </c>
       <c r="W48">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y48">
-        <v>4.046825647888202</v>
+        <v>3.734580553470949</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5397,22 +5397,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.103901783300662</v>
+        <v>0.1038092848827798</v>
       </c>
       <c r="C49">
-        <v>52.65559468478362</v>
+        <v>51.82547842854716</v>
       </c>
       <c r="D49">
-        <v>81.20029468478361</v>
+        <v>81.29027842854715</v>
       </c>
       <c r="E49">
-        <v>41.83470000000001</v>
+        <v>42.7548</v>
       </c>
       <c r="F49">
-        <v>43.2447</v>
+        <v>44.1648</v>
       </c>
       <c r="G49">
         <v>14.7</v>
@@ -5433,28 +5433,28 @@
         <v>9.9</v>
       </c>
       <c r="M49">
-        <v>2.65090011</v>
+        <v>2.70730224</v>
       </c>
       <c r="N49">
-        <v>7.24909989</v>
+        <v>7.19269776</v>
       </c>
       <c r="O49">
-        <v>1.449819978</v>
+        <v>1.438539552</v>
       </c>
       <c r="P49">
-        <v>5.799279912</v>
+        <v>5.754158208</v>
       </c>
       <c r="Q49">
-        <v>6.499279912</v>
+        <v>6.454158207999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1525527986804944</v>
+        <v>0.1543655478514996</v>
       </c>
       <c r="T49">
-        <v>2.08081074516253</v>
+        <v>2.116144600573679</v>
       </c>
       <c r="U49">
         <v>0.0613</v>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.734580553470949</v>
+        <v>3.656776791940304</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5479,22 +5479,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1038092848827798</v>
+        <v>0.1037167864648975</v>
       </c>
       <c r="C50">
-        <v>51.82547842854716</v>
+        <v>50.99556182816328</v>
       </c>
       <c r="D50">
-        <v>81.29027842854715</v>
+        <v>81.38046182816328</v>
       </c>
       <c r="E50">
-        <v>42.7548</v>
+        <v>43.6749</v>
       </c>
       <c r="F50">
-        <v>44.16479999999999</v>
+        <v>45.0849</v>
       </c>
       <c r="G50">
         <v>14.7</v>
@@ -5515,28 +5515,28 @@
         <v>9.9</v>
       </c>
       <c r="M50">
-        <v>2.70730224</v>
+        <v>2.76370437</v>
       </c>
       <c r="N50">
-        <v>7.192697760000001</v>
+        <v>7.136295630000001</v>
       </c>
       <c r="O50">
-        <v>1.438539552</v>
+        <v>1.427259126</v>
       </c>
       <c r="P50">
-        <v>5.754158208000001</v>
+        <v>5.709036504000001</v>
       </c>
       <c r="Q50">
-        <v>6.454158208</v>
+        <v>6.409036504</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1543655478514996</v>
+        <v>0.1562493852252893</v>
       </c>
       <c r="T50">
-        <v>2.116144600573679</v>
+        <v>2.152864097373499</v>
       </c>
       <c r="U50">
         <v>0.0613</v>
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.656776791940305</v>
+        <v>3.582148694145605</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5561,22 +5561,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1037167864648975</v>
+        <v>0.1036242880470153</v>
       </c>
       <c r="C51">
-        <v>50.99556182816328</v>
+        <v>50.16584554886434</v>
       </c>
       <c r="D51">
-        <v>81.38046182816328</v>
+        <v>81.47084554886433</v>
       </c>
       <c r="E51">
-        <v>43.6749</v>
+        <v>44.595</v>
       </c>
       <c r="F51">
-        <v>45.0849</v>
+        <v>46.005</v>
       </c>
       <c r="G51">
         <v>14.7</v>
@@ -5597,28 +5597,28 @@
         <v>9.9</v>
       </c>
       <c r="M51">
-        <v>2.76370437</v>
+        <v>2.8201065</v>
       </c>
       <c r="N51">
-        <v>7.136295630000001</v>
+        <v>7.079893500000001</v>
       </c>
       <c r="O51">
-        <v>1.427259126</v>
+        <v>1.4159787</v>
       </c>
       <c r="P51">
-        <v>5.709036504000001</v>
+        <v>5.663914800000001</v>
       </c>
       <c r="Q51">
-        <v>6.409036504</v>
+        <v>6.3639148</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1562493852252893</v>
+        <v>0.1582085760940305</v>
       </c>
       <c r="T51">
-        <v>2.152864097373499</v>
+        <v>2.191052374045313</v>
       </c>
       <c r="U51">
         <v>0.0613</v>
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.582148694145605</v>
+        <v>3.510505720262693</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1036242880470153</v>
+        <v>0.104674189629133</v>
       </c>
       <c r="C52">
-        <v>50.16584554886434</v>
+        <v>48.23149327400809</v>
       </c>
       <c r="D52">
-        <v>81.47084554886433</v>
+        <v>80.45659327400809</v>
       </c>
       <c r="E52">
-        <v>44.595</v>
+        <v>45.5151</v>
       </c>
       <c r="F52">
-        <v>46.005</v>
+        <v>46.92509999999999</v>
       </c>
       <c r="G52">
         <v>14.7</v>
@@ -5679,45 +5679,45 @@
         <v>9.9</v>
       </c>
       <c r="M52">
-        <v>2.8201065</v>
+        <v>3.00789891</v>
       </c>
       <c r="N52">
-        <v>7.079893500000001</v>
+        <v>6.892101090000001</v>
       </c>
       <c r="O52">
-        <v>1.4159787</v>
+        <v>1.378420218</v>
       </c>
       <c r="P52">
-        <v>5.663914800000001</v>
+        <v>5.513680872</v>
       </c>
       <c r="Q52">
-        <v>6.3639148</v>
+        <v>6.213680871999999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1582085760940305</v>
+        <v>0.1602477339370062</v>
       </c>
       <c r="T52">
-        <v>2.191052374045313</v>
+        <v>2.230799355887405</v>
       </c>
       <c r="U52">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V52">
         <v>0.2</v>
       </c>
       <c r="W52">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y52">
-        <v>3.510505720262693</v>
+        <v>3.291334016275168</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5725,22 +5725,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.104674189629133</v>
+        <v>0.1046040912112508</v>
       </c>
       <c r="C53">
-        <v>48.23149327400809</v>
+        <v>47.37832409714458</v>
       </c>
       <c r="D53">
-        <v>80.45659327400809</v>
+        <v>80.52352409714457</v>
       </c>
       <c r="E53">
-        <v>45.5151</v>
+        <v>46.4352</v>
       </c>
       <c r="F53">
-        <v>46.92509999999999</v>
+        <v>47.8452</v>
       </c>
       <c r="G53">
         <v>14.7</v>
@@ -5761,28 +5761,28 @@
         <v>9.9</v>
       </c>
       <c r="M53">
-        <v>3.00789891</v>
+        <v>3.06687732</v>
       </c>
       <c r="N53">
-        <v>6.892101090000001</v>
+        <v>6.833122680000001</v>
       </c>
       <c r="O53">
-        <v>1.378420218</v>
+        <v>1.366624536</v>
       </c>
       <c r="P53">
-        <v>5.513680872</v>
+        <v>5.466498144000001</v>
       </c>
       <c r="Q53">
-        <v>6.213680871999999</v>
+        <v>6.166498144</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1602477339370062</v>
+        <v>0.1623718566901058</v>
       </c>
       <c r="T53">
-        <v>2.230799355887405</v>
+        <v>2.272202461972917</v>
       </c>
       <c r="U53">
         <v>0.0641</v>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.291334016275168</v>
+        <v>3.2280391313468</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5807,22 +5807,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1046040912112508</v>
+        <v>0.1045339927933685</v>
       </c>
       <c r="C54">
-        <v>47.37832409714458</v>
+        <v>46.52526637080716</v>
       </c>
       <c r="D54">
-        <v>80.52352409714457</v>
+        <v>80.59056637080715</v>
       </c>
       <c r="E54">
-        <v>46.4352</v>
+        <v>47.3553</v>
       </c>
       <c r="F54">
-        <v>47.8452</v>
+        <v>48.7653</v>
       </c>
       <c r="G54">
         <v>14.7</v>
@@ -5843,28 +5843,28 @@
         <v>9.9</v>
       </c>
       <c r="M54">
-        <v>3.06687732</v>
+        <v>3.12585573</v>
       </c>
       <c r="N54">
-        <v>6.833122680000001</v>
+        <v>6.774144270000001</v>
       </c>
       <c r="O54">
-        <v>1.366624536</v>
+        <v>1.354828854</v>
       </c>
       <c r="P54">
-        <v>5.466498144000001</v>
+        <v>5.419315416000001</v>
       </c>
       <c r="Q54">
-        <v>6.166498144</v>
+        <v>6.119315416</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1623718566901058</v>
+        <v>0.1645863676454649</v>
       </c>
       <c r="T54">
-        <v>2.272202461972917</v>
+        <v>2.315367402359941</v>
       </c>
       <c r="U54">
         <v>0.0641</v>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.2280391313468</v>
+        <v>3.167132732642143</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5889,22 +5889,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1045339927933685</v>
+        <v>0.1044638943754863</v>
       </c>
       <c r="C55">
-        <v>46.52526637080716</v>
+        <v>45.67232037360222</v>
       </c>
       <c r="D55">
-        <v>80.59056637080715</v>
+        <v>80.65772037360222</v>
       </c>
       <c r="E55">
-        <v>47.3553</v>
+        <v>48.2754</v>
       </c>
       <c r="F55">
-        <v>48.7653</v>
+        <v>49.6854</v>
       </c>
       <c r="G55">
         <v>14.7</v>
@@ -5925,28 +5925,28 @@
         <v>9.9</v>
       </c>
       <c r="M55">
-        <v>3.12585573</v>
+        <v>3.18483414</v>
       </c>
       <c r="N55">
-        <v>6.774144270000001</v>
+        <v>6.71516586</v>
       </c>
       <c r="O55">
-        <v>1.354828854</v>
+        <v>1.343033172</v>
       </c>
       <c r="P55">
-        <v>5.419315416000001</v>
+        <v>5.372132688</v>
       </c>
       <c r="Q55">
-        <v>6.119315416</v>
+        <v>6.072132687999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1645863676454649</v>
+        <v>0.1668971616858397</v>
       </c>
       <c r="T55">
-        <v>2.315367402359941</v>
+        <v>2.360409079285531</v>
       </c>
       <c r="U55">
         <v>0.0641</v>
@@ -5963,7 +5963,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.167132732642143</v>
+        <v>3.108482126482103</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5971,22 +5971,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1044638943754863</v>
+        <v>0.104393795957604</v>
       </c>
       <c r="C56">
-        <v>45.67232037360222</v>
+        <v>44.81948638506551</v>
       </c>
       <c r="D56">
-        <v>80.65772037360222</v>
+        <v>80.72498638506551</v>
       </c>
       <c r="E56">
-        <v>48.2754</v>
+        <v>49.1955</v>
       </c>
       <c r="F56">
-        <v>49.6854</v>
+        <v>50.6055</v>
       </c>
       <c r="G56">
         <v>14.7</v>
@@ -6007,28 +6007,28 @@
         <v>9.9</v>
       </c>
       <c r="M56">
-        <v>3.18483414</v>
+        <v>3.24381255</v>
       </c>
       <c r="N56">
-        <v>6.71516586</v>
+        <v>6.65618745</v>
       </c>
       <c r="O56">
-        <v>1.343033172</v>
+        <v>1.33123749</v>
       </c>
       <c r="P56">
-        <v>5.372132688</v>
+        <v>5.32494996</v>
       </c>
       <c r="Q56">
-        <v>6.072132687999999</v>
+        <v>6.024949959999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1668971616858397</v>
+        <v>0.1693106576835645</v>
       </c>
       <c r="T56">
-        <v>2.360409079285531</v>
+        <v>2.407452608518925</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.108482126482103</v>
+        <v>3.051964269636974</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6053,22 +6053,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.104393795957604</v>
+        <v>0.1078180975397217</v>
       </c>
       <c r="C57">
-        <v>44.81948638506551</v>
+        <v>40.73944118294798</v>
       </c>
       <c r="D57">
-        <v>80.72498638506551</v>
+        <v>77.56504118294798</v>
       </c>
       <c r="E57">
-        <v>49.1955</v>
+        <v>50.1156</v>
       </c>
       <c r="F57">
-        <v>50.6055</v>
+        <v>51.5256</v>
       </c>
       <c r="G57">
         <v>14.7</v>
@@ -6089,45 +6089,45 @@
         <v>9.9</v>
       </c>
       <c r="M57">
-        <v>3.24381255</v>
+        <v>3.70469064</v>
       </c>
       <c r="N57">
-        <v>6.65618745</v>
+        <v>6.19530936</v>
       </c>
       <c r="O57">
-        <v>1.33123749</v>
+        <v>1.239061872</v>
       </c>
       <c r="P57">
-        <v>5.32494996</v>
+        <v>4.956247488000001</v>
       </c>
       <c r="Q57">
-        <v>6.024949959999999</v>
+        <v>5.656247488</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1693106576835645</v>
+        <v>0.1718338580448222</v>
       </c>
       <c r="T57">
-        <v>2.407452608518925</v>
+        <v>2.4566344799902</v>
       </c>
       <c r="U57">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V57">
         <v>0.2</v>
       </c>
       <c r="W57">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y57">
-        <v>3.051964269636974</v>
+        <v>2.67228790795876</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6135,22 +6135,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1078180975397217</v>
+        <v>0.1078103991218395</v>
       </c>
       <c r="C58">
-        <v>40.73944118294798</v>
+        <v>39.82616779612476</v>
       </c>
       <c r="D58">
-        <v>77.56504118294798</v>
+        <v>77.57186779612476</v>
       </c>
       <c r="E58">
-        <v>50.1156</v>
+        <v>51.03570000000001</v>
       </c>
       <c r="F58">
-        <v>51.5256</v>
+        <v>52.4457</v>
       </c>
       <c r="G58">
         <v>14.7</v>
@@ -6171,28 +6171,28 @@
         <v>9.9</v>
       </c>
       <c r="M58">
-        <v>3.70469064</v>
+        <v>3.77084583</v>
       </c>
       <c r="N58">
-        <v>6.19530936</v>
+        <v>6.12915417</v>
       </c>
       <c r="O58">
-        <v>1.239061872</v>
+        <v>1.225830834</v>
       </c>
       <c r="P58">
-        <v>4.956247488000001</v>
+        <v>4.903323336</v>
       </c>
       <c r="Q58">
-        <v>5.656247488</v>
+        <v>5.603323335999999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1718338580448222</v>
+        <v>0.1744744165624174</v>
       </c>
       <c r="T58">
-        <v>2.4566344799902</v>
+        <v>2.508103880367116</v>
       </c>
       <c r="U58">
         <v>0.07190000000000001</v>
@@ -6209,7 +6209,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.67228790795876</v>
+        <v>2.625405663959484</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6217,22 +6217,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1078103991218395</v>
+        <v>0.1078027007039572</v>
       </c>
       <c r="C59">
-        <v>39.82616779612476</v>
+        <v>38.91289561104781</v>
       </c>
       <c r="D59">
-        <v>77.57186779612476</v>
+        <v>77.57869561104781</v>
       </c>
       <c r="E59">
-        <v>51.03570000000001</v>
+        <v>51.9558</v>
       </c>
       <c r="F59">
-        <v>52.4457</v>
+        <v>53.3658</v>
       </c>
       <c r="G59">
         <v>14.7</v>
@@ -6253,28 +6253,28 @@
         <v>9.9</v>
       </c>
       <c r="M59">
-        <v>3.77084583</v>
+        <v>3.83700102</v>
       </c>
       <c r="N59">
-        <v>6.12915417</v>
+        <v>6.06299898</v>
       </c>
       <c r="O59">
-        <v>1.225830834</v>
+        <v>1.212599796</v>
       </c>
       <c r="P59">
-        <v>4.903323336</v>
+        <v>4.850399184</v>
       </c>
       <c r="Q59">
-        <v>5.603323335999999</v>
+        <v>5.550399183999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1744744165624174</v>
+        <v>0.1772407159618029</v>
       </c>
       <c r="T59">
-        <v>2.508103880367116</v>
+        <v>2.562024204571504</v>
       </c>
       <c r="U59">
         <v>0.07190000000000001</v>
@@ -6291,7 +6291,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.625405663959484</v>
+        <v>2.580140049063631</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6299,22 +6299,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1078027007039572</v>
+        <v>0.107795002286075</v>
       </c>
       <c r="C60">
-        <v>38.91289561104782</v>
+        <v>37.99962462803449</v>
       </c>
       <c r="D60">
-        <v>77.57869561104781</v>
+        <v>77.58552462803448</v>
       </c>
       <c r="E60">
-        <v>51.9558</v>
+        <v>52.87589999999999</v>
       </c>
       <c r="F60">
-        <v>53.36579999999999</v>
+        <v>54.28589999999999</v>
       </c>
       <c r="G60">
         <v>14.7</v>
@@ -6335,28 +6335,28 @@
         <v>9.9</v>
       </c>
       <c r="M60">
-        <v>3.83700102</v>
+        <v>3.90315621</v>
       </c>
       <c r="N60">
-        <v>6.062998980000001</v>
+        <v>5.996843790000001</v>
       </c>
       <c r="O60">
-        <v>1.212599796</v>
+        <v>1.199368758</v>
       </c>
       <c r="P60">
-        <v>4.850399184</v>
+        <v>4.797475032</v>
       </c>
       <c r="Q60">
-        <v>5.550399184</v>
+        <v>5.497475032</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1772407159618029</v>
+        <v>0.1801419567953048</v>
       </c>
       <c r="T60">
-        <v>2.562024204571503</v>
+        <v>2.618574788493179</v>
       </c>
       <c r="U60">
         <v>0.07190000000000001</v>
@@ -6373,7 +6373,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.580140049063631</v>
+        <v>2.536408861791366</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6381,22 +6381,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.107795002286075</v>
+        <v>0.1096593038681927</v>
       </c>
       <c r="C61">
-        <v>37.99962462803449</v>
+        <v>35.46013834447918</v>
       </c>
       <c r="D61">
-        <v>77.58552462803448</v>
+        <v>75.96613834447918</v>
       </c>
       <c r="E61">
-        <v>52.87589999999999</v>
+        <v>53.796</v>
       </c>
       <c r="F61">
-        <v>54.28589999999999</v>
+        <v>55.206</v>
       </c>
       <c r="G61">
         <v>14.7</v>
@@ -6417,45 +6417,45 @@
         <v>9.9</v>
       </c>
       <c r="M61">
-        <v>3.90315621</v>
+        <v>4.1846148</v>
       </c>
       <c r="N61">
-        <v>5.996843790000001</v>
+        <v>5.7153852</v>
       </c>
       <c r="O61">
-        <v>1.199368758</v>
+        <v>1.14307704</v>
       </c>
       <c r="P61">
-        <v>4.797475032</v>
+        <v>4.57230816</v>
       </c>
       <c r="Q61">
-        <v>5.497475032</v>
+        <v>5.27230816</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1801419567953048</v>
+        <v>0.1831882596704818</v>
       </c>
       <c r="T61">
-        <v>2.618574788493179</v>
+        <v>2.677952901610938</v>
       </c>
       <c r="U61">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V61">
         <v>0.2</v>
       </c>
       <c r="W61">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y61">
-        <v>2.536408861791366</v>
+        <v>2.365809154046867</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6463,22 +6463,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1096593038681927</v>
+        <v>0.1096828054503104</v>
       </c>
       <c r="C62">
-        <v>35.46013834447918</v>
+        <v>34.52005553805587</v>
       </c>
       <c r="D62">
-        <v>75.96613834447918</v>
+        <v>75.94615553805586</v>
       </c>
       <c r="E62">
-        <v>53.796</v>
+        <v>54.7161</v>
       </c>
       <c r="F62">
-        <v>55.206</v>
+        <v>56.12609999999999</v>
       </c>
       <c r="G62">
         <v>14.7</v>
@@ -6499,28 +6499,28 @@
         <v>9.9</v>
       </c>
       <c r="M62">
-        <v>4.1846148</v>
+        <v>4.25435838</v>
       </c>
       <c r="N62">
-        <v>5.7153852</v>
+        <v>5.64564162</v>
       </c>
       <c r="O62">
-        <v>1.14307704</v>
+        <v>1.129128324</v>
       </c>
       <c r="P62">
-        <v>4.57230816</v>
+        <v>4.516513296</v>
       </c>
       <c r="Q62">
-        <v>5.27230816</v>
+        <v>5.216513296</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1831882596704818</v>
+        <v>0.1863907832059242</v>
       </c>
       <c r="T62">
-        <v>2.677952901610938</v>
+        <v>2.740376046170633</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.365809154046867</v>
+        <v>2.327025397423148</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6545,22 +6545,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1096828054503104</v>
+        <v>0.1097063070324282</v>
       </c>
       <c r="C63">
-        <v>34.52005553805587</v>
+        <v>33.57998324177692</v>
       </c>
       <c r="D63">
-        <v>75.94615553805586</v>
+        <v>75.92618324177691</v>
       </c>
       <c r="E63">
-        <v>54.7161</v>
+        <v>55.6362</v>
       </c>
       <c r="F63">
-        <v>56.12609999999999</v>
+        <v>57.04619999999999</v>
       </c>
       <c r="G63">
         <v>14.7</v>
@@ -6581,28 +6581,28 @@
         <v>9.9</v>
       </c>
       <c r="M63">
-        <v>4.25435838</v>
+        <v>4.32410196</v>
       </c>
       <c r="N63">
-        <v>5.64564162</v>
+        <v>5.57589804</v>
       </c>
       <c r="O63">
-        <v>1.129128324</v>
+        <v>1.115179608</v>
       </c>
       <c r="P63">
-        <v>4.516513296</v>
+        <v>4.460718432</v>
       </c>
       <c r="Q63">
-        <v>5.216513296</v>
+        <v>5.160718431999999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1863907832059242</v>
+        <v>0.1897618606116532</v>
       </c>
       <c r="T63">
-        <v>2.740376046170633</v>
+        <v>2.806084619391366</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6619,7 +6619,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.327025397423148</v>
+        <v>2.289492729722775</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6627,22 +6627,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1097063070324282</v>
+        <v>0.109729808614546</v>
       </c>
       <c r="C64">
-        <v>33.57998324177692</v>
+        <v>32.6399214473527</v>
       </c>
       <c r="D64">
-        <v>75.92618324177691</v>
+        <v>75.90622144735269</v>
       </c>
       <c r="E64">
-        <v>55.6362</v>
+        <v>56.5563</v>
       </c>
       <c r="F64">
-        <v>57.04619999999999</v>
+        <v>57.9663</v>
       </c>
       <c r="G64">
         <v>14.7</v>
@@ -6663,28 +6663,28 @@
         <v>9.9</v>
       </c>
       <c r="M64">
-        <v>4.32410196</v>
+        <v>4.39384554</v>
       </c>
       <c r="N64">
-        <v>5.57589804</v>
+        <v>5.50615446</v>
       </c>
       <c r="O64">
-        <v>1.115179608</v>
+        <v>1.101230892</v>
       </c>
       <c r="P64">
-        <v>4.460718432</v>
+        <v>4.404923568</v>
       </c>
       <c r="Q64">
-        <v>5.160718431999999</v>
+        <v>5.104923567999999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1897618606116532</v>
+        <v>0.1933151584176918</v>
       </c>
       <c r="T64">
-        <v>2.806084619391366</v>
+        <v>2.875345007380786</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.289492729722775</v>
+        <v>2.253151575282731</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.109729808614546</v>
+        <v>0.1097533101966637</v>
       </c>
       <c r="C65">
-        <v>32.6399214473527</v>
+        <v>31.69987014650221</v>
       </c>
       <c r="D65">
-        <v>75.90622144735269</v>
+        <v>75.8862701465022</v>
       </c>
       <c r="E65">
-        <v>56.5563</v>
+        <v>57.4764</v>
       </c>
       <c r="F65">
-        <v>57.9663</v>
+        <v>58.88639999999999</v>
       </c>
       <c r="G65">
         <v>14.7</v>
@@ -6745,28 +6745,28 @@
         <v>9.9</v>
       </c>
       <c r="M65">
-        <v>4.39384554</v>
+        <v>4.46358912</v>
       </c>
       <c r="N65">
-        <v>5.50615446</v>
+        <v>5.43641088</v>
       </c>
       <c r="O65">
-        <v>1.101230892</v>
+        <v>1.087282176</v>
       </c>
       <c r="P65">
-        <v>4.404923568</v>
+        <v>4.349128704</v>
       </c>
       <c r="Q65">
-        <v>5.104923567999999</v>
+        <v>5.049128703999999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1933151584176918</v>
+        <v>0.1970658616573991</v>
       </c>
       <c r="T65">
-        <v>2.875345007380786</v>
+        <v>2.948453194702953</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6783,7 +6783,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.253151575282731</v>
+        <v>2.217946081918938</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6791,22 +6791,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1097533101966637</v>
+        <v>0.1097768117787814</v>
       </c>
       <c r="C66">
-        <v>31.69987014650221</v>
+        <v>30.75982933095323</v>
       </c>
       <c r="D66">
-        <v>75.8862701465022</v>
+        <v>75.86632933095322</v>
       </c>
       <c r="E66">
-        <v>57.4764</v>
+        <v>58.3965</v>
       </c>
       <c r="F66">
-        <v>58.88639999999999</v>
+        <v>59.80649999999999</v>
       </c>
       <c r="G66">
         <v>14.7</v>
@@ -6827,28 +6827,28 @@
         <v>9.9</v>
       </c>
       <c r="M66">
-        <v>4.46358912</v>
+        <v>4.5333327</v>
       </c>
       <c r="N66">
-        <v>5.43641088</v>
+        <v>5.3666673</v>
       </c>
       <c r="O66">
-        <v>1.087282176</v>
+        <v>1.07333346</v>
       </c>
       <c r="P66">
-        <v>4.349128704</v>
+        <v>4.293333840000001</v>
       </c>
       <c r="Q66">
-        <v>5.049128703999999</v>
+        <v>4.99333384</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1970658616573991</v>
+        <v>0.2010308907965184</v>
       </c>
       <c r="T66">
-        <v>2.948453194702953</v>
+        <v>3.025738992729242</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.217946081918938</v>
+        <v>2.183823834504801</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6873,22 +6873,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1097768117787814</v>
+        <v>0.1098003133608992</v>
       </c>
       <c r="C67">
-        <v>30.75982933095323</v>
+        <v>29.81979899244211</v>
       </c>
       <c r="D67">
-        <v>75.86632933095322</v>
+        <v>75.8463989924421</v>
       </c>
       <c r="E67">
-        <v>58.3965</v>
+        <v>59.3166</v>
       </c>
       <c r="F67">
-        <v>59.80649999999999</v>
+        <v>60.7266</v>
       </c>
       <c r="G67">
         <v>14.7</v>
@@ -6909,28 +6909,28 @@
         <v>9.9</v>
       </c>
       <c r="M67">
-        <v>4.5333327</v>
+        <v>4.60307628</v>
       </c>
       <c r="N67">
-        <v>5.3666673</v>
+        <v>5.296923720000001</v>
       </c>
       <c r="O67">
-        <v>1.07333346</v>
+        <v>1.059384744</v>
       </c>
       <c r="P67">
-        <v>4.293333840000001</v>
+        <v>4.237538976000001</v>
       </c>
       <c r="Q67">
-        <v>4.99333384</v>
+        <v>4.937538976</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2010308907965184</v>
+        <v>0.2052291569438211</v>
       </c>
       <c r="T67">
-        <v>3.025738992729242</v>
+        <v>3.107571014168843</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.183823834504801</v>
+        <v>2.150735594588061</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6955,22 +6955,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1098003133608992</v>
+        <v>0.1098238149430169</v>
       </c>
       <c r="C68">
-        <v>29.81979899244211</v>
+        <v>28.87977912271403</v>
       </c>
       <c r="D68">
-        <v>75.8463989924421</v>
+        <v>75.82647912271402</v>
       </c>
       <c r="E68">
-        <v>59.3166</v>
+        <v>60.2367</v>
       </c>
       <c r="F68">
-        <v>60.7266</v>
+        <v>61.6467</v>
       </c>
       <c r="G68">
         <v>14.7</v>
@@ -6991,28 +6991,28 @@
         <v>9.9</v>
       </c>
       <c r="M68">
-        <v>4.60307628</v>
+        <v>4.67281986</v>
       </c>
       <c r="N68">
-        <v>5.296923720000001</v>
+        <v>5.227180140000001</v>
       </c>
       <c r="O68">
-        <v>1.059384744</v>
+        <v>1.045436028</v>
       </c>
       <c r="P68">
-        <v>4.237538976000001</v>
+        <v>4.181744112000001</v>
       </c>
       <c r="Q68">
-        <v>4.937538976</v>
+        <v>4.881744112</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2052291569438211</v>
+        <v>0.2096818634636877</v>
       </c>
       <c r="T68">
-        <v>3.107571014168843</v>
+        <v>3.194362552059329</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -7029,7 +7029,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.150735594588061</v>
+        <v>2.118635063325553</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7037,22 +7037,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1098238149430169</v>
+        <v>0.1098473165251347</v>
       </c>
       <c r="C69">
-        <v>28.87977912271403</v>
+        <v>27.93976971352275</v>
       </c>
       <c r="D69">
-        <v>75.82647912271402</v>
+        <v>75.80656971352275</v>
       </c>
       <c r="E69">
-        <v>60.2367</v>
+        <v>61.1568</v>
       </c>
       <c r="F69">
-        <v>61.6467</v>
+        <v>62.5668</v>
       </c>
       <c r="G69">
         <v>14.7</v>
@@ -7073,28 +7073,28 @@
         <v>9.9</v>
       </c>
       <c r="M69">
-        <v>4.67281986</v>
+        <v>4.742563440000001</v>
       </c>
       <c r="N69">
-        <v>5.227180140000001</v>
+        <v>5.15743656</v>
       </c>
       <c r="O69">
-        <v>1.045436028</v>
+        <v>1.031487312</v>
       </c>
       <c r="P69">
-        <v>4.181744112000001</v>
+        <v>4.125949248</v>
       </c>
       <c r="Q69">
-        <v>4.881744112</v>
+        <v>4.825949247999999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2096818634636877</v>
+        <v>0.2144128641410458</v>
       </c>
       <c r="T69">
-        <v>3.194362552059329</v>
+        <v>3.28657856106797</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -7111,7 +7111,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.118635063325553</v>
+        <v>2.087478665335471</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7119,22 +7119,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1098473165251347</v>
+        <v>0.1098708181072524</v>
       </c>
       <c r="C70">
-        <v>27.93976971352275</v>
+        <v>26.99977075663069</v>
       </c>
       <c r="D70">
-        <v>75.80656971352275</v>
+        <v>75.78667075663068</v>
       </c>
       <c r="E70">
-        <v>61.1568</v>
+        <v>62.0769</v>
       </c>
       <c r="F70">
-        <v>62.5668</v>
+        <v>63.4869</v>
       </c>
       <c r="G70">
         <v>14.7</v>
@@ -7155,28 +7155,28 @@
         <v>9.9</v>
       </c>
       <c r="M70">
-        <v>4.742563440000001</v>
+        <v>4.81230702</v>
       </c>
       <c r="N70">
-        <v>5.15743656</v>
+        <v>5.08769298</v>
       </c>
       <c r="O70">
-        <v>1.031487312</v>
+        <v>1.017538596</v>
       </c>
       <c r="P70">
-        <v>4.125949248</v>
+        <v>4.070154384</v>
       </c>
       <c r="Q70">
-        <v>4.825949247999999</v>
+        <v>4.770154384</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2144128641410458</v>
+        <v>0.2194490906685562</v>
       </c>
       <c r="T70">
-        <v>3.28657856106797</v>
+        <v>3.384743990012653</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.087478665335471</v>
+        <v>2.057225351345102</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7201,22 +7201,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1098708181072524</v>
+        <v>0.1098943196893702</v>
       </c>
       <c r="C71">
-        <v>26.99977075663069</v>
+        <v>26.05978224380894</v>
       </c>
       <c r="D71">
-        <v>75.78667075663068</v>
+        <v>75.76678224380893</v>
       </c>
       <c r="E71">
-        <v>62.0769</v>
+        <v>62.997</v>
       </c>
       <c r="F71">
-        <v>63.4869</v>
+        <v>64.407</v>
       </c>
       <c r="G71">
         <v>14.7</v>
@@ -7237,28 +7237,28 @@
         <v>9.9</v>
       </c>
       <c r="M71">
-        <v>4.81230702</v>
+        <v>4.8820506</v>
       </c>
       <c r="N71">
-        <v>5.08769298</v>
+        <v>5.0179494</v>
       </c>
       <c r="O71">
-        <v>1.017538596</v>
+        <v>1.00358988</v>
       </c>
       <c r="P71">
-        <v>4.070154384</v>
+        <v>4.01435952</v>
       </c>
       <c r="Q71">
-        <v>4.770154384</v>
+        <v>4.714359519999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2194490906685562</v>
+        <v>0.2248210656312339</v>
       </c>
       <c r="T71">
-        <v>3.384743990012653</v>
+        <v>3.489453780886981</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.057225351345102</v>
+        <v>2.027836417754457</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7283,22 +7283,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1098943196893702</v>
+        <v>0.1179834212714879</v>
       </c>
       <c r="C72">
-        <v>26.05978224380894</v>
+        <v>18.86292758095625</v>
       </c>
       <c r="D72">
-        <v>75.76678224380893</v>
+        <v>69.49002758095625</v>
       </c>
       <c r="E72">
-        <v>62.997</v>
+        <v>63.9171</v>
       </c>
       <c r="F72">
-        <v>64.407</v>
+        <v>65.3271</v>
       </c>
       <c r="G72">
         <v>14.7</v>
@@ -7319,45 +7319,45 @@
         <v>9.9</v>
       </c>
       <c r="M72">
-        <v>4.8820506</v>
+        <v>5.879439</v>
       </c>
       <c r="N72">
-        <v>5.0179494</v>
+        <v>4.020561000000001</v>
       </c>
       <c r="O72">
-        <v>1.00358988</v>
+        <v>0.8041122000000002</v>
       </c>
       <c r="P72">
-        <v>4.01435952</v>
+        <v>3.216448800000001</v>
       </c>
       <c r="Q72">
-        <v>4.714359519999999</v>
+        <v>3.9164488</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2248210656312339</v>
+        <v>0.2305635216258204</v>
       </c>
       <c r="T72">
-        <v>3.489453780886981</v>
+        <v>3.601384936649194</v>
       </c>
       <c r="U72">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V72">
         <v>0.2</v>
       </c>
       <c r="W72">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y72">
-        <v>2.027836417754457</v>
+        <v>1.683834120908475</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7365,22 +7365,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1179834212714879</v>
+        <v>0.1181205228536056</v>
       </c>
       <c r="C73">
-        <v>18.86292758095627</v>
+        <v>17.84539334008733</v>
       </c>
       <c r="D73">
-        <v>69.49002758095625</v>
+        <v>69.39259334008732</v>
       </c>
       <c r="E73">
-        <v>63.91709999999999</v>
+        <v>64.8372</v>
       </c>
       <c r="F73">
-        <v>65.32709999999999</v>
+        <v>66.24719999999999</v>
       </c>
       <c r="G73">
         <v>14.7</v>
@@ -7401,28 +7401,28 @@
         <v>9.9</v>
       </c>
       <c r="M73">
-        <v>5.879438999999999</v>
+        <v>5.962247999999999</v>
       </c>
       <c r="N73">
-        <v>4.020561000000002</v>
+        <v>3.937752000000001</v>
       </c>
       <c r="O73">
-        <v>0.8041122000000004</v>
+        <v>0.7875504000000003</v>
       </c>
       <c r="P73">
-        <v>3.216448800000001</v>
+        <v>3.150201600000001</v>
       </c>
       <c r="Q73">
-        <v>3.9164488</v>
+        <v>3.850201600000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2305635216258203</v>
+        <v>0.2367161530485916</v>
       </c>
       <c r="T73">
-        <v>3.601384936649193</v>
+        <v>3.721311174965849</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7439,7 +7439,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.683834120908475</v>
+        <v>1.660447535895857</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7447,22 +7447,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1181205228536056</v>
+        <v>0.1182576244357234</v>
       </c>
       <c r="C74">
-        <v>17.84539334008733</v>
+        <v>16.82813194812091</v>
       </c>
       <c r="D74">
-        <v>69.39259334008732</v>
+        <v>69.29543194812091</v>
       </c>
       <c r="E74">
-        <v>64.8372</v>
+        <v>65.7573</v>
       </c>
       <c r="F74">
-        <v>66.24719999999999</v>
+        <v>67.1673</v>
       </c>
       <c r="G74">
         <v>14.7</v>
@@ -7483,28 +7483,28 @@
         <v>9.9</v>
       </c>
       <c r="M74">
-        <v>5.962247999999999</v>
+        <v>6.045057</v>
       </c>
       <c r="N74">
-        <v>3.937752000000001</v>
+        <v>3.854943</v>
       </c>
       <c r="O74">
-        <v>0.7875504000000003</v>
+        <v>0.7709886000000001</v>
       </c>
       <c r="P74">
-        <v>3.150201600000001</v>
+        <v>3.083954400000001</v>
       </c>
       <c r="Q74">
-        <v>3.850201600000001</v>
+        <v>3.7839544</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2367161530485916</v>
+        <v>0.2433245349471236</v>
       </c>
       <c r="T74">
-        <v>3.721311174965849</v>
+        <v>3.850120838342998</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.660447535895857</v>
+        <v>1.637701679239749</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7529,22 +7529,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1182576244357234</v>
+        <v>0.1183947260178411</v>
       </c>
       <c r="C75">
-        <v>16.82813194812091</v>
+        <v>15.8111422605554</v>
       </c>
       <c r="D75">
-        <v>69.29543194812091</v>
+        <v>69.19854226055539</v>
       </c>
       <c r="E75">
-        <v>65.7573</v>
+        <v>66.67739999999999</v>
       </c>
       <c r="F75">
-        <v>67.1673</v>
+        <v>68.08739999999999</v>
       </c>
       <c r="G75">
         <v>14.7</v>
@@ -7565,28 +7565,28 @@
         <v>9.9</v>
       </c>
       <c r="M75">
-        <v>6.045057</v>
+        <v>6.127865999999999</v>
       </c>
       <c r="N75">
-        <v>3.854943</v>
+        <v>3.772134000000001</v>
       </c>
       <c r="O75">
-        <v>0.7709886000000001</v>
+        <v>0.7544268000000003</v>
       </c>
       <c r="P75">
-        <v>3.083954400000001</v>
+        <v>3.017707200000001</v>
       </c>
       <c r="Q75">
-        <v>3.7839544</v>
+        <v>3.7177072</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2433245349471236</v>
+        <v>0.2504412539147735</v>
       </c>
       <c r="T75">
-        <v>3.850120838342998</v>
+        <v>3.988838937364544</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.637701679239749</v>
+        <v>1.615570575466239</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7611,22 +7611,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1183947260178411</v>
+        <v>0.1185318275999589</v>
       </c>
       <c r="C76">
-        <v>15.8111422605554</v>
+        <v>14.79442313928122</v>
       </c>
       <c r="D76">
-        <v>69.19854226055539</v>
+        <v>69.10192313928121</v>
       </c>
       <c r="E76">
-        <v>66.67739999999999</v>
+        <v>67.5975</v>
       </c>
       <c r="F76">
-        <v>68.08739999999999</v>
+        <v>69.00749999999999</v>
       </c>
       <c r="G76">
         <v>14.7</v>
@@ -7647,28 +7647,28 @@
         <v>9.9</v>
       </c>
       <c r="M76">
-        <v>6.127865999999999</v>
+        <v>6.210674999999999</v>
       </c>
       <c r="N76">
-        <v>3.772134000000001</v>
+        <v>3.689325000000001</v>
       </c>
       <c r="O76">
-        <v>0.7544268000000003</v>
+        <v>0.7378650000000002</v>
       </c>
       <c r="P76">
-        <v>3.017707200000001</v>
+        <v>2.951460000000001</v>
       </c>
       <c r="Q76">
-        <v>3.7177072</v>
+        <v>3.65146</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2504412539147735</v>
+        <v>0.2581273103998355</v>
       </c>
       <c r="T76">
-        <v>3.988838937364544</v>
+        <v>4.138654484307814</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.615570575466239</v>
+        <v>1.594029634460023</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7693,22 +7693,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1185318275999589</v>
+        <v>0.1186689291820766</v>
       </c>
       <c r="C77">
-        <v>14.79442313928122</v>
+        <v>13.77797345253637</v>
       </c>
       <c r="D77">
-        <v>69.10192313928121</v>
+        <v>69.00557345253637</v>
       </c>
       <c r="E77">
-        <v>67.5975</v>
+        <v>68.5176</v>
       </c>
       <c r="F77">
-        <v>69.00749999999999</v>
+        <v>69.9276</v>
       </c>
       <c r="G77">
         <v>14.7</v>
@@ -7729,28 +7729,28 @@
         <v>9.9</v>
       </c>
       <c r="M77">
-        <v>6.210674999999999</v>
+        <v>6.293483999999999</v>
       </c>
       <c r="N77">
-        <v>3.689325000000001</v>
+        <v>3.606516000000001</v>
       </c>
       <c r="O77">
-        <v>0.7378650000000002</v>
+        <v>0.7213032000000003</v>
       </c>
       <c r="P77">
-        <v>2.951460000000001</v>
+        <v>2.885212800000001</v>
       </c>
       <c r="Q77">
-        <v>3.65146</v>
+        <v>3.5852128</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2581273103998355</v>
+        <v>0.2664538715919859</v>
       </c>
       <c r="T77">
-        <v>4.138654484307814</v>
+        <v>4.300954660163022</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.594029634460023</v>
+        <v>1.573055560322391</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7775,22 +7775,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1186689291820766</v>
+        <v>0.1188060307641944</v>
       </c>
       <c r="C78">
-        <v>13.77797345253637</v>
+        <v>12.76179207486217</v>
       </c>
       <c r="D78">
-        <v>69.00557345253637</v>
+        <v>68.90949207486216</v>
       </c>
       <c r="E78">
-        <v>68.5176</v>
+        <v>69.43769999999999</v>
       </c>
       <c r="F78">
-        <v>69.9276</v>
+        <v>70.84769999999999</v>
       </c>
       <c r="G78">
         <v>14.7</v>
@@ -7811,28 +7811,28 @@
         <v>9.9</v>
       </c>
       <c r="M78">
-        <v>6.293483999999999</v>
+        <v>6.376292999999999</v>
       </c>
       <c r="N78">
-        <v>3.606516000000001</v>
+        <v>3.523707000000002</v>
       </c>
       <c r="O78">
-        <v>0.7213032000000003</v>
+        <v>0.7047414000000004</v>
       </c>
       <c r="P78">
-        <v>2.885212800000001</v>
+        <v>2.818965600000001</v>
       </c>
       <c r="Q78">
-        <v>3.5852128</v>
+        <v>3.5189656</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2664538715919859</v>
+        <v>0.2755044815834538</v>
       </c>
       <c r="T78">
-        <v>4.300954660163022</v>
+        <v>4.477367894788249</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7849,7 +7849,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.573055560322391</v>
+        <v>1.552626267331191</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7857,22 +7857,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1188060307641944</v>
+        <v>0.1189431323463121</v>
       </c>
       <c r="C79">
-        <v>12.76179207486217</v>
+        <v>11.74587788705941</v>
       </c>
       <c r="D79">
-        <v>68.90949207486216</v>
+        <v>68.8136778870594</v>
       </c>
       <c r="E79">
-        <v>69.43769999999999</v>
+        <v>70.3578</v>
       </c>
       <c r="F79">
-        <v>70.84769999999999</v>
+        <v>71.76779999999999</v>
       </c>
       <c r="G79">
         <v>14.7</v>
@@ -7893,28 +7893,28 @@
         <v>9.9</v>
       </c>
       <c r="M79">
-        <v>6.376292999999999</v>
+        <v>6.459101999999999</v>
       </c>
       <c r="N79">
-        <v>3.523707000000002</v>
+        <v>3.440898000000002</v>
       </c>
       <c r="O79">
-        <v>0.7047414000000004</v>
+        <v>0.6881796000000003</v>
       </c>
       <c r="P79">
-        <v>2.818965600000001</v>
+        <v>2.752718400000001</v>
       </c>
       <c r="Q79">
-        <v>3.5189656</v>
+        <v>3.452718400000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2755044815834538</v>
+        <v>0.2853778743014186</v>
       </c>
       <c r="T79">
-        <v>4.477367894788249</v>
+        <v>4.669818696197587</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.552626267331191</v>
+        <v>1.532720802365406</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7939,22 +7939,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1189431323463121</v>
+        <v>0.1190802339284298</v>
       </c>
       <c r="C80">
-        <v>11.74587788705941</v>
+        <v>10.73022977614498</v>
       </c>
       <c r="D80">
-        <v>68.8136778870594</v>
+        <v>68.71812977614498</v>
       </c>
       <c r="E80">
-        <v>70.3578</v>
+        <v>71.2779</v>
       </c>
       <c r="F80">
-        <v>71.76779999999999</v>
+        <v>72.6879</v>
       </c>
       <c r="G80">
         <v>14.7</v>
@@ -7975,28 +7975,28 @@
         <v>9.9</v>
       </c>
       <c r="M80">
-        <v>6.459101999999999</v>
+        <v>6.541911</v>
       </c>
       <c r="N80">
-        <v>3.440898000000002</v>
+        <v>3.358089000000001</v>
       </c>
       <c r="O80">
-        <v>0.6881796000000003</v>
+        <v>0.6716178000000002</v>
       </c>
       <c r="P80">
-        <v>2.752718400000001</v>
+        <v>2.686471200000001</v>
       </c>
       <c r="Q80">
-        <v>3.452718400000001</v>
+        <v>3.3864712</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2853778743014186</v>
+        <v>0.2961915901353803</v>
       </c>
       <c r="T80">
-        <v>4.669818696197587</v>
+        <v>4.880598145360196</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -8013,7 +8013,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.532720802365406</v>
+        <v>1.51331927322154</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8021,22 +8021,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1190802339284298</v>
+        <v>0.1583753844143371</v>
       </c>
       <c r="C81">
-        <v>10.73022977614498</v>
+        <v>-9.752136116543639</v>
       </c>
       <c r="D81">
-        <v>68.71812977614498</v>
+        <v>49.15586388345635</v>
       </c>
       <c r="E81">
-        <v>71.2779</v>
+        <v>72.19799999999999</v>
       </c>
       <c r="F81">
-        <v>72.6879</v>
+        <v>73.60799999999999</v>
       </c>
       <c r="G81">
         <v>14.7</v>
@@ -8057,45 +8057,45 @@
         <v>9.9</v>
       </c>
       <c r="M81">
-        <v>6.541911</v>
+        <v>10.8056544</v>
       </c>
       <c r="N81">
-        <v>3.358089000000001</v>
+        <v>-0.9056543999999995</v>
       </c>
       <c r="O81">
-        <v>0.6716178000000002</v>
+        <v>-0.1811308799999999</v>
       </c>
       <c r="P81">
-        <v>2.686471200000001</v>
+        <v>-0.7245235199999996</v>
       </c>
       <c r="Q81">
-        <v>3.3864712</v>
+        <v>-0.02452352000000035</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2961915901353803</v>
+        <v>0.3122739223977371</v>
       </c>
       <c r="T81">
-        <v>4.880598145360196</v>
+        <v>5.194072735182829</v>
       </c>
       <c r="U81">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.2</v>
+        <v>0.1832373983754284</v>
       </c>
       <c r="W81">
-        <v>0.07199999999999999</v>
+        <v>0.1199007499184871</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y81">
-        <v>1.51331927322154</v>
+        <v>0.9161869918771417</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8103,22 +8103,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1583753844143371</v>
+        <v>0.1593853844143371</v>
       </c>
       <c r="C82">
-        <v>-9.752136116543639</v>
+        <v>-11.02929466389951</v>
       </c>
       <c r="D82">
-        <v>49.15586388345635</v>
+        <v>48.79880533610049</v>
       </c>
       <c r="E82">
-        <v>72.19799999999999</v>
+        <v>73.1181</v>
       </c>
       <c r="F82">
-        <v>73.60799999999999</v>
+        <v>74.52809999999999</v>
       </c>
       <c r="G82">
         <v>14.7</v>
@@ -8139,37 +8139,37 @@
         <v>9.9</v>
       </c>
       <c r="M82">
-        <v>10.8056544</v>
+        <v>10.94072508</v>
       </c>
       <c r="N82">
-        <v>-0.9056543999999995</v>
+        <v>-1.04072508</v>
       </c>
       <c r="O82">
-        <v>-0.1811308799999999</v>
+        <v>-0.2081450159999999</v>
       </c>
       <c r="P82">
-        <v>-0.7245235199999996</v>
+        <v>-0.8325800639999997</v>
       </c>
       <c r="Q82">
-        <v>-0.02452352000000035</v>
+        <v>-0.1325800640000004</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3122739223977371</v>
+        <v>0.3262988656818285</v>
       </c>
       <c r="T82">
-        <v>5.194072735182829</v>
+        <v>5.467444984402978</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.1832373983754284</v>
+        <v>0.180975208272028</v>
       </c>
       <c r="W82">
-        <v>0.1199007499184871</v>
+        <v>0.1202328394256663</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.9161869918771417</v>
+        <v>0.90487604136014</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8185,22 +8185,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1593853844143371</v>
+        <v>0.1603953844143371</v>
       </c>
       <c r="C83">
-        <v>-11.02929466389951</v>
+        <v>-12.30130341197145</v>
       </c>
       <c r="D83">
-        <v>48.79880533610049</v>
+        <v>48.44689658802856</v>
       </c>
       <c r="E83">
-        <v>73.1181</v>
+        <v>74.0382</v>
       </c>
       <c r="F83">
-        <v>74.52809999999999</v>
+        <v>75.4482</v>
       </c>
       <c r="G83">
         <v>14.7</v>
@@ -8221,37 +8221,37 @@
         <v>9.9</v>
       </c>
       <c r="M83">
-        <v>10.94072508</v>
+        <v>11.07579576</v>
       </c>
       <c r="N83">
-        <v>-1.04072508</v>
+        <v>-1.175795760000002</v>
       </c>
       <c r="O83">
-        <v>-0.2081450159999999</v>
+        <v>-0.2351591520000003</v>
       </c>
       <c r="P83">
-        <v>-0.8325800639999997</v>
+        <v>-0.9406366080000013</v>
       </c>
       <c r="Q83">
-        <v>-0.1325800640000004</v>
+        <v>-0.240636608000002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3262988656818285</v>
+        <v>0.3418821359974856</v>
       </c>
       <c r="T83">
-        <v>5.467444984402978</v>
+        <v>5.771191927980921</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.180975208272028</v>
+        <v>0.1787681935370032</v>
       </c>
       <c r="W83">
-        <v>0.1202328394256663</v>
+        <v>0.1205568291887679</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.90487604136014</v>
+        <v>0.8938409676850161</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8267,22 +8267,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1603953844143371</v>
+        <v>0.1614053844143371</v>
       </c>
       <c r="C84">
-        <v>-12.30130341197145</v>
+        <v>-13.56827297519013</v>
       </c>
       <c r="D84">
-        <v>48.44689658802856</v>
+        <v>48.10002702480988</v>
       </c>
       <c r="E84">
-        <v>74.0382</v>
+        <v>74.95830000000001</v>
       </c>
       <c r="F84">
-        <v>75.4482</v>
+        <v>76.3683</v>
       </c>
       <c r="G84">
         <v>14.7</v>
@@ -8303,37 +8303,37 @@
         <v>9.9</v>
       </c>
       <c r="M84">
-        <v>11.07579576</v>
+        <v>11.21086644</v>
       </c>
       <c r="N84">
-        <v>-1.175795760000002</v>
+        <v>-1.310866440000002</v>
       </c>
       <c r="O84">
-        <v>-0.2351591520000003</v>
+        <v>-0.2621732880000003</v>
       </c>
       <c r="P84">
-        <v>-0.9406366080000013</v>
+        <v>-1.048693152000001</v>
       </c>
       <c r="Q84">
-        <v>-0.240636608000002</v>
+        <v>-0.3486931520000021</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3418821359974856</v>
+        <v>0.3592987322326319</v>
       </c>
       <c r="T84">
-        <v>5.771191927980921</v>
+        <v>6.110673806097446</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.1787681935370032</v>
+        <v>0.1766143598799309</v>
       </c>
       <c r="W84">
-        <v>0.1205568291887679</v>
+        <v>0.1208730119696262</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8938409676850161</v>
+        <v>0.8830717993996545</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8349,22 +8349,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1614053844143371</v>
+        <v>0.1624153844143371</v>
       </c>
       <c r="C85">
-        <v>-13.56827297519013</v>
+        <v>-14.83031082260256</v>
       </c>
       <c r="D85">
-        <v>48.10002702480988</v>
+        <v>47.75808917739744</v>
       </c>
       <c r="E85">
-        <v>74.95830000000001</v>
+        <v>75.8784</v>
       </c>
       <c r="F85">
-        <v>76.3683</v>
+        <v>77.2884</v>
       </c>
       <c r="G85">
         <v>14.7</v>
@@ -8385,37 +8385,37 @@
         <v>9.9</v>
       </c>
       <c r="M85">
-        <v>11.21086644</v>
+        <v>11.34593712</v>
       </c>
       <c r="N85">
-        <v>-1.310866440000002</v>
+        <v>-1.44593712</v>
       </c>
       <c r="O85">
-        <v>-0.2621732880000003</v>
+        <v>-0.289187424</v>
       </c>
       <c r="P85">
-        <v>-1.048693152000001</v>
+        <v>-1.156749696</v>
       </c>
       <c r="Q85">
-        <v>-0.3486931520000021</v>
+        <v>-0.4567496960000006</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3592987322326319</v>
+        <v>0.3788924029971715</v>
       </c>
       <c r="T85">
-        <v>6.110673806097446</v>
+        <v>6.492590918978538</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.1766143598799309</v>
+        <v>0.1745118079765984</v>
       </c>
       <c r="W85">
-        <v>0.1208730119696262</v>
+        <v>0.1211816665890354</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8830717993996545</v>
+        <v>0.8725590398829921</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8431,22 +8431,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1624153844143371</v>
+        <v>0.1634253844143371</v>
       </c>
       <c r="C86">
-        <v>-14.83031082260256</v>
+        <v>-16.08752138888377</v>
       </c>
       <c r="D86">
-        <v>47.75808917739744</v>
+        <v>47.42097861111622</v>
       </c>
       <c r="E86">
-        <v>75.8784</v>
+        <v>76.79849999999999</v>
       </c>
       <c r="F86">
-        <v>77.2884</v>
+        <v>78.20849999999999</v>
       </c>
       <c r="G86">
         <v>14.7</v>
@@ -8467,37 +8467,37 @@
         <v>9.9</v>
       </c>
       <c r="M86">
-        <v>11.34593712</v>
+        <v>11.4810078</v>
       </c>
       <c r="N86">
-        <v>-1.44593712</v>
+        <v>-1.581007799999998</v>
       </c>
       <c r="O86">
-        <v>-0.289187424</v>
+        <v>-0.3162015599999997</v>
       </c>
       <c r="P86">
-        <v>-1.156749696</v>
+        <v>-1.264806239999999</v>
       </c>
       <c r="Q86">
-        <v>-0.4567496960000006</v>
+        <v>-0.5648062399999993</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3788924029971713</v>
+        <v>0.4010985631969827</v>
       </c>
       <c r="T86">
-        <v>6.492590918978534</v>
+        <v>6.925430313577102</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.1745118079765984</v>
+        <v>0.1724587278827561</v>
       </c>
       <c r="W86">
-        <v>0.1211816665890354</v>
+        <v>0.1214830587468114</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8725590398829921</v>
+        <v>0.8622936394137806</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8513,22 +8513,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1634253844143371</v>
+        <v>0.1644353844143371</v>
       </c>
       <c r="C87">
-        <v>-16.08752138888377</v>
+        <v>-17.34000618068005</v>
       </c>
       <c r="D87">
-        <v>47.42097861111622</v>
+        <v>47.08859381931995</v>
       </c>
       <c r="E87">
-        <v>76.79849999999999</v>
+        <v>77.7186</v>
       </c>
       <c r="F87">
-        <v>78.20849999999999</v>
+        <v>79.12859999999999</v>
       </c>
       <c r="G87">
         <v>14.7</v>
@@ -8549,37 +8549,37 @@
         <v>9.9</v>
       </c>
       <c r="M87">
-        <v>11.4810078</v>
+        <v>11.61607848</v>
       </c>
       <c r="N87">
-        <v>-1.581007799999998</v>
+        <v>-1.71607848</v>
       </c>
       <c r="O87">
-        <v>-0.3162015599999997</v>
+        <v>-0.3432156960000001</v>
       </c>
       <c r="P87">
-        <v>-1.264806239999999</v>
+        <v>-1.372862784</v>
       </c>
       <c r="Q87">
-        <v>-0.5648062399999993</v>
+        <v>-0.6728627840000008</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4010985631969827</v>
+        <v>0.4264770319967671</v>
       </c>
       <c r="T87">
-        <v>6.925430313577102</v>
+        <v>7.420103907404037</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.1724587278827561</v>
+        <v>0.1704533938376078</v>
       </c>
       <c r="W87">
-        <v>0.1214830587468114</v>
+        <v>0.1217774417846392</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8587,7 +8587,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8622936394137806</v>
+        <v>0.8522669691880387</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8595,22 +8595,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1644353844143371</v>
+        <v>0.1654453844143371</v>
       </c>
       <c r="C88">
-        <v>-17.34000618068005</v>
+        <v>-18.58786387851082</v>
       </c>
       <c r="D88">
-        <v>47.08859381931995</v>
+        <v>46.76083612148918</v>
       </c>
       <c r="E88">
-        <v>77.7186</v>
+        <v>78.6387</v>
       </c>
       <c r="F88">
-        <v>79.12859999999999</v>
+        <v>80.0487</v>
       </c>
       <c r="G88">
         <v>14.7</v>
@@ -8631,37 +8631,37 @@
         <v>9.9</v>
       </c>
       <c r="M88">
-        <v>11.61607848</v>
+        <v>11.75114916</v>
       </c>
       <c r="N88">
-        <v>-1.71607848</v>
+        <v>-1.85114916</v>
       </c>
       <c r="O88">
-        <v>-0.3432156960000001</v>
+        <v>-0.3702298320000001</v>
       </c>
       <c r="P88">
-        <v>-1.372862784</v>
+        <v>-1.480919328</v>
       </c>
       <c r="Q88">
-        <v>-0.6728627840000008</v>
+        <v>-0.7809193280000009</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4264770319967671</v>
+        <v>0.455759880611903</v>
       </c>
       <c r="T88">
-        <v>7.420103907404037</v>
+        <v>7.990881131050502</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.1704533938376078</v>
+        <v>0.1684941594256812</v>
       </c>
       <c r="W88">
-        <v>0.1217774417846392</v>
+        <v>0.12206505739631</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8522669691880387</v>
+        <v>0.8424707971284061</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8677,22 +8677,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1654453844143371</v>
+        <v>0.1664553844143371</v>
       </c>
       <c r="C89">
-        <v>-18.58786387851082</v>
+        <v>-19.83119043444431</v>
       </c>
       <c r="D89">
-        <v>46.76083612148918</v>
+        <v>46.43760956555568</v>
       </c>
       <c r="E89">
-        <v>78.6387</v>
+        <v>79.55879999999999</v>
       </c>
       <c r="F89">
-        <v>80.0487</v>
+        <v>80.96879999999999</v>
       </c>
       <c r="G89">
         <v>14.7</v>
@@ -8713,37 +8713,37 @@
         <v>9.9</v>
       </c>
       <c r="M89">
-        <v>11.75114916</v>
+        <v>11.88621984</v>
       </c>
       <c r="N89">
-        <v>-1.85114916</v>
+        <v>-1.986219839999999</v>
       </c>
       <c r="O89">
-        <v>-0.3702298320000001</v>
+        <v>-0.3972439679999997</v>
       </c>
       <c r="P89">
-        <v>-1.480919328</v>
+        <v>-1.588975871999999</v>
       </c>
       <c r="Q89">
-        <v>-0.7809193280000009</v>
+        <v>-0.8889758719999996</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.455759880611903</v>
+        <v>0.4899232039962283</v>
       </c>
       <c r="T89">
-        <v>7.990881131050502</v>
+        <v>8.656787891971378</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.1684941594256812</v>
+        <v>0.1665794530685712</v>
       </c>
       <c r="W89">
-        <v>0.12206505739631</v>
+        <v>0.1223461362895338</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8424707971284061</v>
+        <v>0.8328972653428561</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8759,22 +8759,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1664553844143371</v>
+        <v>0.1674653844143371</v>
       </c>
       <c r="C90">
-        <v>-19.83119043444431</v>
+        <v>-21.07007916575014</v>
       </c>
       <c r="D90">
-        <v>46.43760956555568</v>
+        <v>46.11882083424985</v>
       </c>
       <c r="E90">
-        <v>79.55879999999999</v>
+        <v>80.4789</v>
       </c>
       <c r="F90">
-        <v>80.96879999999999</v>
+        <v>81.88889999999999</v>
       </c>
       <c r="G90">
         <v>14.7</v>
@@ -8795,37 +8795,37 @@
         <v>9.9</v>
       </c>
       <c r="M90">
-        <v>11.88621984</v>
+        <v>12.02129052</v>
       </c>
       <c r="N90">
-        <v>-1.986219839999999</v>
+        <v>-2.121290520000001</v>
       </c>
       <c r="O90">
-        <v>-0.3972439679999997</v>
+        <v>-0.4242581040000001</v>
       </c>
       <c r="P90">
-        <v>-1.588975871999999</v>
+        <v>-1.697032416</v>
       </c>
       <c r="Q90">
-        <v>-0.8889758719999996</v>
+        <v>-0.997032416000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4899232039962283</v>
+        <v>0.5302980407231582</v>
       </c>
       <c r="T90">
-        <v>8.656787891971378</v>
+        <v>9.443768609423323</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.1665794530685712</v>
+        <v>0.1647077738206097</v>
       </c>
       <c r="W90">
-        <v>0.1223461362895338</v>
+        <v>0.1226208988031345</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8328972653428561</v>
+        <v>0.8235388691030486</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8841,22 +8841,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1674653844143371</v>
+        <v>0.1684753844143371</v>
       </c>
       <c r="C91">
-        <v>-21.07007916575014</v>
+        <v>-22.30462084472047</v>
       </c>
       <c r="D91">
-        <v>46.11882083424985</v>
+        <v>45.80437915527953</v>
       </c>
       <c r="E91">
-        <v>80.4789</v>
+        <v>81.399</v>
       </c>
       <c r="F91">
-        <v>81.88889999999999</v>
+        <v>82.809</v>
       </c>
       <c r="G91">
         <v>14.7</v>
@@ -8877,37 +8877,37 @@
         <v>9.9</v>
       </c>
       <c r="M91">
-        <v>12.02129052</v>
+        <v>12.1563612</v>
       </c>
       <c r="N91">
-        <v>-2.121290520000001</v>
+        <v>-2.256361200000001</v>
       </c>
       <c r="O91">
-        <v>-0.4242581040000001</v>
+        <v>-0.4512722400000002</v>
       </c>
       <c r="P91">
-        <v>-1.697032416</v>
+        <v>-1.80508896</v>
       </c>
       <c r="Q91">
-        <v>-0.997032416000001</v>
+        <v>-1.105088960000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5302980407231582</v>
+        <v>0.578747844795474</v>
       </c>
       <c r="T91">
-        <v>9.443768609423323</v>
+        <v>10.38814547036566</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.1647077738206097</v>
+        <v>0.1628776874448252</v>
       </c>
       <c r="W91">
-        <v>0.1226208988031345</v>
+        <v>0.1228895554830997</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8235388691030486</v>
+        <v>0.8143884372241259</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8923,22 +8923,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1684753844143371</v>
+        <v>0.1694853844143371</v>
       </c>
       <c r="C92">
-        <v>-22.30462084472047</v>
+        <v>-23.53490378484186</v>
       </c>
       <c r="D92">
-        <v>45.80437915527953</v>
+        <v>45.49419621515813</v>
       </c>
       <c r="E92">
-        <v>81.399</v>
+        <v>82.31909999999999</v>
       </c>
       <c r="F92">
-        <v>82.809</v>
+        <v>83.72909999999999</v>
       </c>
       <c r="G92">
         <v>14.7</v>
@@ -8959,37 +8959,37 @@
         <v>9.9</v>
       </c>
       <c r="M92">
-        <v>12.1563612</v>
+        <v>12.29143188</v>
       </c>
       <c r="N92">
-        <v>-2.256361200000001</v>
+        <v>-2.391431879999999</v>
       </c>
       <c r="O92">
-        <v>-0.4512722400000002</v>
+        <v>-0.4782863759999998</v>
       </c>
       <c r="P92">
-        <v>-1.80508896</v>
+        <v>-1.913145503999999</v>
       </c>
       <c r="Q92">
-        <v>-1.105088960000001</v>
+        <v>-1.213145504</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.578747844795474</v>
+        <v>0.6379642719949712</v>
       </c>
       <c r="T92">
-        <v>10.38814547036566</v>
+        <v>11.54238385596184</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.1628776874448252</v>
+        <v>0.1610878227476293</v>
       </c>
       <c r="W92">
-        <v>0.1228895554830997</v>
+        <v>0.123152307620648</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8143884372241259</v>
+        <v>0.8054391137381466</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9005,22 +9005,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1694853844143371</v>
+        <v>0.2226372316301008</v>
       </c>
       <c r="C93">
-        <v>-23.53490378484186</v>
+        <v>-36.40819703406416</v>
       </c>
       <c r="D93">
-        <v>45.49419621515813</v>
+        <v>33.54100296593584</v>
       </c>
       <c r="E93">
-        <v>82.31909999999999</v>
+        <v>83.2392</v>
       </c>
       <c r="F93">
-        <v>83.72909999999999</v>
+        <v>84.64919999999999</v>
       </c>
       <c r="G93">
         <v>14.7</v>
@@ -9041,45 +9041,45 @@
         <v>9.9</v>
       </c>
       <c r="M93">
-        <v>12.29143188</v>
+        <v>16.99755936</v>
       </c>
       <c r="N93">
-        <v>-2.391431879999999</v>
+        <v>-7.09755936</v>
       </c>
       <c r="O93">
-        <v>-0.4782863759999998</v>
+        <v>-1.419511872</v>
       </c>
       <c r="P93">
-        <v>-1.913145503999999</v>
+        <v>-5.678047488</v>
       </c>
       <c r="Q93">
-        <v>-1.213145504</v>
+        <v>-4.978047488000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6379642719949712</v>
+        <v>0.7427578961913894</v>
       </c>
       <c r="T93">
-        <v>11.54238385596184</v>
+        <v>13.58500664382018</v>
       </c>
       <c r="U93">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1610878227476293</v>
+        <v>0.1164873119760648</v>
       </c>
       <c r="W93">
-        <v>0.123152307620648</v>
+        <v>0.1774093477552062</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y93">
-        <v>0.8054391137381466</v>
+        <v>0.5824365598803238</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9087,22 +9087,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2226372316301008</v>
+        <v>0.2241872316301008</v>
       </c>
       <c r="C94">
-        <v>-36.40819703406416</v>
+        <v>-37.58333359925817</v>
       </c>
       <c r="D94">
-        <v>33.54100296593584</v>
+        <v>33.28596640074183</v>
       </c>
       <c r="E94">
-        <v>83.2392</v>
+        <v>84.1593</v>
       </c>
       <c r="F94">
-        <v>84.64919999999999</v>
+        <v>85.5693</v>
       </c>
       <c r="G94">
         <v>14.7</v>
@@ -9123,37 +9123,37 @@
         <v>9.9</v>
       </c>
       <c r="M94">
-        <v>16.99755936</v>
+        <v>17.18231544</v>
       </c>
       <c r="N94">
-        <v>-7.09755936</v>
+        <v>-7.28231544</v>
       </c>
       <c r="O94">
-        <v>-1.419511872</v>
+        <v>-1.456463088</v>
       </c>
       <c r="P94">
-        <v>-5.678047488</v>
+        <v>-5.825852352</v>
       </c>
       <c r="Q94">
-        <v>-4.978047488000001</v>
+        <v>-5.125852352000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7427578961913894</v>
+        <v>0.8423233099330166</v>
       </c>
       <c r="T94">
-        <v>13.58500664382018</v>
+        <v>15.52572187865163</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1164873119760648</v>
+        <v>0.1152347602343867</v>
       </c>
       <c r="W94">
-        <v>0.1774093477552062</v>
+        <v>0.1776608601449352</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5824365598803238</v>
+        <v>0.5761738011719333</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9169,22 +9169,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2241872316301008</v>
+        <v>0.2257372316301008</v>
       </c>
       <c r="C95">
-        <v>-37.58333359925817</v>
+        <v>-38.75462097676699</v>
       </c>
       <c r="D95">
-        <v>33.28596640074183</v>
+        <v>33.03477902323301</v>
       </c>
       <c r="E95">
-        <v>84.1593</v>
+        <v>85.07940000000001</v>
       </c>
       <c r="F95">
-        <v>85.5693</v>
+        <v>86.4894</v>
       </c>
       <c r="G95">
         <v>14.7</v>
@@ -9205,37 +9205,37 @@
         <v>9.9</v>
       </c>
       <c r="M95">
-        <v>17.18231544</v>
+        <v>17.36707152</v>
       </c>
       <c r="N95">
-        <v>-7.28231544</v>
+        <v>-7.467071519999999</v>
       </c>
       <c r="O95">
-        <v>-1.456463088</v>
+        <v>-1.493414304</v>
       </c>
       <c r="P95">
-        <v>-5.825852352</v>
+        <v>-5.973657215999999</v>
       </c>
       <c r="Q95">
-        <v>-5.125852352000001</v>
+        <v>-5.273657216</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8423233099330166</v>
+        <v>0.975077194921853</v>
       </c>
       <c r="T95">
-        <v>15.52572187865163</v>
+        <v>18.11334219176024</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1152347602343867</v>
+        <v>0.1140088585297656</v>
       </c>
       <c r="W95">
-        <v>0.1776608601449352</v>
+        <v>0.1779070212072231</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5761738011719333</v>
+        <v>0.5700442926488276</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9251,22 +9251,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2257372316301008</v>
+        <v>0.2272872316301008</v>
       </c>
       <c r="C96">
-        <v>-38.75462097676699</v>
+        <v>-39.92214565580491</v>
       </c>
       <c r="D96">
-        <v>33.03477902323301</v>
+        <v>32.78735434419509</v>
       </c>
       <c r="E96">
-        <v>85.07940000000001</v>
+        <v>85.9995</v>
       </c>
       <c r="F96">
-        <v>86.4894</v>
+        <v>87.40949999999999</v>
       </c>
       <c r="G96">
         <v>14.7</v>
@@ -9287,37 +9287,37 @@
         <v>9.9</v>
       </c>
       <c r="M96">
-        <v>17.36707152</v>
+        <v>17.5518276</v>
       </c>
       <c r="N96">
-        <v>-7.467071519999999</v>
+        <v>-7.651827599999999</v>
       </c>
       <c r="O96">
-        <v>-1.493414304</v>
+        <v>-1.53036552</v>
       </c>
       <c r="P96">
-        <v>-5.973657215999999</v>
+        <v>-6.121462079999999</v>
       </c>
       <c r="Q96">
-        <v>-5.273657216</v>
+        <v>-5.42146208</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.975077194921853</v>
+        <v>1.160932633906224</v>
       </c>
       <c r="T96">
-        <v>18.11334219176024</v>
+        <v>21.7360106301123</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1140088585297656</v>
+        <v>0.1128087652820838</v>
       </c>
       <c r="W96">
-        <v>0.1779070212072231</v>
+        <v>0.1781479999313576</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5700442926488276</v>
+        <v>0.5640438264104191</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9333,22 +9333,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2272872316301008</v>
+        <v>0.2288372316301008</v>
       </c>
       <c r="C97">
-        <v>-39.92214565580491</v>
+        <v>-41.0859915536933</v>
       </c>
       <c r="D97">
-        <v>32.78735434419509</v>
+        <v>32.54360844630669</v>
       </c>
       <c r="E97">
-        <v>85.9995</v>
+        <v>86.9196</v>
       </c>
       <c r="F97">
-        <v>87.40949999999999</v>
+        <v>88.3296</v>
       </c>
       <c r="G97">
         <v>14.7</v>
@@ -9369,37 +9369,37 @@
         <v>9.9</v>
       </c>
       <c r="M97">
-        <v>17.5518276</v>
+        <v>17.73658368</v>
       </c>
       <c r="N97">
-        <v>-7.651827599999999</v>
+        <v>-7.836583679999999</v>
       </c>
       <c r="O97">
-        <v>-1.53036552</v>
+        <v>-1.567316736</v>
       </c>
       <c r="P97">
-        <v>-6.121462079999999</v>
+        <v>-6.269266943999999</v>
       </c>
       <c r="Q97">
-        <v>-5.42146208</v>
+        <v>-5.569266944</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.160932633906224</v>
+        <v>1.439715792382781</v>
       </c>
       <c r="T97">
-        <v>21.7360106301123</v>
+        <v>27.17001328764039</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1128087652820838</v>
+        <v>0.1116336739770621</v>
       </c>
       <c r="W97">
-        <v>0.1781479999313576</v>
+        <v>0.1783839582654059</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5640438264104191</v>
+        <v>0.5581683698853104</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9415,22 +9415,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2288372316301008</v>
+        <v>0.2303872316301008</v>
       </c>
       <c r="C98">
-        <v>-41.0859915536933</v>
+        <v>-42.24624011075431</v>
       </c>
       <c r="D98">
-        <v>32.54360844630668</v>
+        <v>32.30345988924568</v>
       </c>
       <c r="E98">
-        <v>86.91959999999999</v>
+        <v>87.83969999999999</v>
       </c>
       <c r="F98">
-        <v>88.32959999999999</v>
+        <v>89.24969999999999</v>
       </c>
       <c r="G98">
         <v>14.7</v>
@@ -9451,37 +9451,37 @@
         <v>9.9</v>
       </c>
       <c r="M98">
-        <v>17.73658368</v>
+        <v>17.92133976</v>
       </c>
       <c r="N98">
-        <v>-7.836583679999999</v>
+        <v>-8.021339759999998</v>
       </c>
       <c r="O98">
-        <v>-1.567316736</v>
+        <v>-1.604267952</v>
       </c>
       <c r="P98">
-        <v>-6.269266943999999</v>
+        <v>-6.417071807999998</v>
       </c>
       <c r="Q98">
-        <v>-5.569266944</v>
+        <v>-5.717071807999999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.439715792382777</v>
+        <v>1.904354389843703</v>
       </c>
       <c r="T98">
-        <v>27.17001328764031</v>
+        <v>36.22668438352042</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1116336739770621</v>
+        <v>0.1104828113587419</v>
       </c>
       <c r="W98">
-        <v>0.1783839582654059</v>
+        <v>0.1786150514791646</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9489,7 +9489,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5581683698853104</v>
+        <v>0.5524140567937093</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9497,22 +9497,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2303872316301008</v>
+        <v>0.2319372316301008</v>
       </c>
       <c r="C99">
-        <v>-42.24624011075431</v>
+        <v>-43.4029703810337</v>
       </c>
       <c r="D99">
-        <v>32.30345988924568</v>
+        <v>32.0668296189663</v>
       </c>
       <c r="E99">
-        <v>87.83969999999999</v>
+        <v>88.7598</v>
       </c>
       <c r="F99">
-        <v>89.24969999999999</v>
+        <v>90.1698</v>
       </c>
       <c r="G99">
         <v>14.7</v>
@@ -9533,37 +9533,37 @@
         <v>9.9</v>
       </c>
       <c r="M99">
-        <v>17.92133976</v>
+        <v>18.10609584</v>
       </c>
       <c r="N99">
-        <v>-8.021339759999998</v>
+        <v>-8.206095839999998</v>
       </c>
       <c r="O99">
-        <v>-1.604267952</v>
+        <v>-1.641219168</v>
       </c>
       <c r="P99">
-        <v>-6.417071807999998</v>
+        <v>-6.564876671999999</v>
       </c>
       <c r="Q99">
-        <v>-5.717071807999999</v>
+        <v>-5.864876671999999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.904354389843703</v>
+        <v>2.833631584765554</v>
       </c>
       <c r="T99">
-        <v>36.22668438352042</v>
+        <v>54.34002657528062</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1104828113587419</v>
+        <v>0.1093554357326323</v>
       </c>
       <c r="W99">
-        <v>0.1786150514791646</v>
+        <v>0.1788414285048874</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5524140567937093</v>
+        <v>0.5467771786631612</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9579,22 +9579,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2319372316301008</v>
+        <v>0.2334872316301008</v>
       </c>
       <c r="C100">
-        <v>-43.4029703810337</v>
+        <v>-44.55625911906544</v>
       </c>
       <c r="D100">
-        <v>32.0668296189663</v>
+        <v>31.83364088093454</v>
       </c>
       <c r="E100">
-        <v>88.7598</v>
+        <v>89.67989999999999</v>
       </c>
       <c r="F100">
-        <v>90.1698</v>
+        <v>91.08989999999999</v>
       </c>
       <c r="G100">
         <v>14.7</v>
@@ -9615,37 +9615,37 @@
         <v>9.9</v>
       </c>
       <c r="M100">
-        <v>18.10609584</v>
+        <v>18.29085192</v>
       </c>
       <c r="N100">
-        <v>-8.206095839999998</v>
+        <v>-8.390851919999998</v>
       </c>
       <c r="O100">
-        <v>-1.641219168</v>
+        <v>-1.678170384</v>
       </c>
       <c r="P100">
-        <v>-6.564876671999999</v>
+        <v>-6.712681535999998</v>
       </c>
       <c r="Q100">
-        <v>-5.864876671999999</v>
+        <v>-6.012681535999999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.833631584765554</v>
+        <v>5.621463169531108</v>
       </c>
       <c r="T100">
-        <v>54.34002657528062</v>
+        <v>108.6800531505612</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1093554357326323</v>
+        <v>0.1082508353716966</v>
       </c>
       <c r="W100">
-        <v>0.1788414285048874</v>
+        <v>0.1790632322573633</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9653,91 +9653,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5467771786631612</v>
+        <v>0.5412541768584829</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2334872316301008</v>
-      </c>
-      <c r="C101">
-        <v>-44.55625911906544</v>
-      </c>
-      <c r="D101">
-        <v>31.83364088093454</v>
-      </c>
-      <c r="E101">
-        <v>89.67989999999999</v>
-      </c>
-      <c r="F101">
-        <v>91.08989999999999</v>
-      </c>
-      <c r="G101">
-        <v>14.7</v>
-      </c>
-      <c r="H101">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>10.6</v>
-      </c>
-      <c r="K101">
-        <v>0.6999999999999993</v>
-      </c>
-      <c r="L101">
-        <v>9.9</v>
-      </c>
-      <c r="M101">
-        <v>18.29085192</v>
-      </c>
-      <c r="N101">
-        <v>-8.390851919999998</v>
-      </c>
-      <c r="O101">
-        <v>-1.678170384</v>
-      </c>
-      <c r="P101">
-        <v>-6.712681535999998</v>
-      </c>
-      <c r="Q101">
-        <v>-6.012681535999999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.621463169531108</v>
-      </c>
-      <c r="T101">
-        <v>108.6800531505612</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1082508353716966</v>
-      </c>
-      <c r="W101">
-        <v>0.1790632322573633</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5412541768584829</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
